--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -632,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -654,58 +654,58 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mmmarc20</v>
+        <v>combintel</v>
       </c>
       <c r="B20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>alvesmidih</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>leandro._bjj</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -727,7 +727,7 @@
         <v>lucasluiz911_mma</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -1326,35 +1326,35 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>edebetim_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>s__simone__</v>
+        <v>edebetim_</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,21 +1382,21 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -1410,69 +1410,69 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>adriano.trator</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>douglasipvr_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -1480,13 +1480,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -1494,35 +1494,35 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -1536,27 +1536,27 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>marcos_tailandess</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>diegopaivajj</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -1578,21 +1578,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1634,21 +1634,21 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -1732,13 +1732,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>maca.mariotti</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>treinaadorrafael</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1774,13 +1774,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -1788,13 +1788,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -1830,41 +1830,41 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>reifernandes</v>
+        <v>030sami</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>benjafloripabjj</v>
+        <v>reifernandes</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,13 +2026,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ismaeldaniell</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ravenrodriguez___</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,35 +2068,35 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>cristianpsicologo</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>xavyeroficial</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>jcchagas_</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>_alcantara.bru</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,13 +3202,13 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -3216,13 +3216,13 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,16 +3426,16 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>odeivisoncardoso</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D217">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -4840,13 +4840,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3">
@@ -4854,13 +4854,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
@@ -4896,7 +4896,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -4910,7 +4910,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -4924,7 +4924,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -5053,7 +5053,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -5075,58 +5075,58 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mmmarc20</v>
+        <v>combintel</v>
       </c>
       <c r="B20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>alvesmidih</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>leandro._bjj</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -5148,7 +5148,7 @@
         <v>lucasluiz911_mma</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -5747,35 +5747,35 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>edebetim_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>s__simone__</v>
+        <v>edebetim_</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -5803,21 +5803,21 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -5831,69 +5831,69 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>adriano.trator</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>douglasipvr_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -5901,13 +5901,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -5915,35 +5915,35 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -5957,27 +5957,27 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>marcos_tailandess</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>diegopaivajj</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -5999,21 +5999,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -6055,21 +6055,21 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -6153,13 +6153,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>maca.mariotti</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -6167,21 +6167,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>treinaadorrafael</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6195,13 +6195,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -6209,13 +6209,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6237,13 +6237,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6251,41 +6251,41 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>reifernandes</v>
+        <v>030sami</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>benjafloripabjj</v>
+        <v>reifernandes</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6447,13 +6447,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -6461,13 +6461,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ismaeldaniell</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ravenrodriguez___</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6489,35 +6489,35 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>cristianpsicologo</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6531,7 +6531,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6559,13 +6559,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6587,7 +6587,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -6839,7 +6839,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>xavyeroficial</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7049,7 +7049,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>jcchagas_</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>_alcantara.bru</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7623,13 +7623,13 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -7637,13 +7637,13 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7749,7 +7749,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -7847,16 +7847,16 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>odeivisoncardoso</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D217">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C4">
         <v>24</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -640,30 +640,30 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>leandro._bjj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -752,30 +752,30 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1438,55 +1438,55 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>douglasipvr_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1508,35 +1508,35 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -1550,41 +1550,41 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>marcos_tailandess</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>diegopaivajj</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -1592,21 +1592,21 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1648,21 +1648,21 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -1746,13 +1746,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>maca.mariotti</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -1760,21 +1760,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>treinaadorrafael</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1788,13 +1788,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -1844,41 +1844,41 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>reifernandes</v>
+        <v>030sami</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>benjafloripabjj</v>
+        <v>reifernandes</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -2054,13 +2054,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ismaeldaniell</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4840,13 +4840,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
@@ -4854,13 +4854,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
@@ -4868,13 +4868,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C4">
         <v>24</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -4924,7 +4924,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -5061,30 +5061,30 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>leandro._bjj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -5173,30 +5173,30 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -5859,55 +5859,55 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>douglasipvr_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -5915,13 +5915,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -5929,35 +5929,35 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -5971,41 +5971,41 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>marcos_tailandess</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>diegopaivajj</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -6013,21 +6013,21 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -6069,21 +6069,21 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -6167,13 +6167,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>maca.mariotti</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -6181,21 +6181,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>treinaadorrafael</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6209,13 +6209,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -6223,13 +6223,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6265,41 +6265,41 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>reifernandes</v>
+        <v>030sami</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>benjafloripabjj</v>
+        <v>reifernandes</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6461,13 +6461,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -6475,13 +6475,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ismaeldaniell</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -475,7 +475,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -632,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -4840,13 +4840,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3">
@@ -4854,13 +4854,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
@@ -4882,7 +4882,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -4896,7 +4896,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -4910,7 +4910,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5053,7 +5053,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D17">
         <v>12</v>
@@ -5179,7 +5179,7 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>5</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D315"/>
+  <dimension ref="A1:D318"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -601,13 +601,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>18</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -1760,13 +1760,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>maca.mariotti</v>
+        <v>graalino</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -1774,41 +1774,41 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>treinaadorrafael</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fernando.mma</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fagnerosensei</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -1844,13 +1844,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>030sami</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -1858,27 +1858,27 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>reifernandes</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -1886,27 +1886,27 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>guiiviieira_</v>
+        <v>reifernandes</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>cshigueo</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>emerson_lucaszx</v>
+        <v>cshigueo</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>mttsm._</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>andrealvess02</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>gildojiu</v>
+        <v>mttsm._</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>kawannsennast</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>yurimartins1_</v>
+        <v>gildojiu</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>matheusteodoro_1</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,13 +2054,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>kael_lyto</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -2068,13 +2068,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ravenrodriguez___</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -2082,21 +2082,21 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D121">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>juanx.pontes</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,21 +2110,21 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>select_from_joao</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>yeslifeacademia</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ojaimerocha</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,13 +2152,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>tonketjudes</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>_eliasffx</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>pdfiv</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>mariaraimundad940</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>gabesantos.13</v>
+        <v>pdfiv</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>euvitormirandaa</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>thompsonborralho</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>frankikolimabjj</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>anahangelica</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>minotaurinho</v>
+        <v>anahangelica</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>lara.rpr</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>codasqueves</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>yan_touro.7766</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>carolinne.xwp</v>
+        <v>codasqueves</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>davicorbella</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>davicorbella</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>artemio_bjj</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>katiaecarreraf</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>geraldocnetomma</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>xavyeroficial</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>maryanagandra</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>eliandropires</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>charlesanthony2466</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>eliandropires</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>draanapaulaponceano</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>saj_photo_miami</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>alternativaremocoes</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>benivalentinn</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>navarro_9430</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>_puroosso88</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>_rayysp</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>cami.terra_</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>gabicardoson</v>
+        <v>_rayysp</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>martta.mariah</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>wlt_miguel</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>pietroshz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>___neller</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>_bety_marcal</v>
+        <v>pietroshz</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>guilhermeefelix__</v>
+        <v>___neller</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>pativinisf</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>judadany</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>andre_alcausa</v>
+        <v>pativinisf</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>_fernunes</v>
+        <v>judadany</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>aloirmarcal</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gilberto_7606</v>
+        <v>_fernunes</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>flazuera14</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>danlouiz.jj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>gabriel_trevelin</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>y.arthur_01</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>muricunha</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>victorhenriquebjj</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>_lsanchess_</v>
+        <v>muricunha</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>__bielgg</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mr__rlk01</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>vitor_buck</v>
+        <v>__bielgg</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>fran.ruys</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>wesley_bjjvc</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>peacegrappler</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>aliferpaulo_</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>jcchagas_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cesar.boanerges</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>alexandreconsentino</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,13 +3216,13 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>rafaela_duaartee</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,13 +3244,13 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>andre.legendre.10</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>phillipe.harry</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>andrejetx</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>leandro_motiv4</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>olga.oliveira013</v>
+        <v>andrejetx</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>leosacraa</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>gutocriativo</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>igorfso_</v>
+        <v>leosacraa</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>lay_roqs</v>
+        <v>igorfso_</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>bigjota.artist</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>mth_fernandes031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,13 +3440,13 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>marinealcausa</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -3454,13 +3454,13 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>emersonriosmma</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -3468,27 +3468,27 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>luizcosta_mma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B220">
         <v>0</v>
       </c>
       <c r="C220">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>michelle_mirele</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B221">
         <v>0</v>
       </c>
       <c r="C221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -3496,49 +3496,49 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>danielfranzesilva</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B222">
         <v>0</v>
       </c>
       <c r="C222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ednilsonkaicai</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B223">
         <v>0</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D223">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>pedro_pavin_</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B224">
         <v>0</v>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>dogodoyfoto</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -3561,18 +3561,18 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B227">
         <v>0</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -3580,21 +3580,21 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>leonardopateira</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
       <c r="C228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>rahikikhalid</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -3608,35 +3608,35 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>manumito.oficial</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>carlosnoelblack</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -3650,63 +3650,63 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>lokomemo_protetores</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>coutz11</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>orlando_alfa09</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>vitorshowman</v>
+        <v>coutz11</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>4lissson</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,35 +3720,35 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>danilofernandescf</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>bryandazuera</v>
+        <v>4lissson</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3757,12 +3757,12 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>fredoctmma</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3771,12 +3771,12 @@
         <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>_kainanlima</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>ricardotofanello</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,28 +4798,70 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
         <v>roginbrito</v>
       </c>
-      <c r="B315">
-        <v>0</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315">
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D315"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D318"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D315"/>
+  <dimension ref="A1:D318"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4882,13 +4924,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -5022,13 +5064,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>18</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -6181,13 +6223,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>maca.mariotti</v>
+        <v>graalino</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -6195,41 +6237,41 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>treinaadorrafael</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fernando.mma</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6237,13 +6279,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6251,13 +6293,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fagnerosensei</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6265,13 +6307,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>030sami</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6279,27 +6321,27 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>reifernandes</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6307,27 +6349,27 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>guiiviieira_</v>
+        <v>reifernandes</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>cshigueo</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6335,7 +6377,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6349,7 +6391,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>emerson_lucaszx</v>
+        <v>cshigueo</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6363,7 +6405,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6377,7 +6419,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>mttsm._</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6391,7 +6433,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>andrealvess02</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6405,7 +6447,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>gildojiu</v>
+        <v>mttsm._</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6419,7 +6461,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>kawannsennast</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6433,7 +6475,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>yurimartins1_</v>
+        <v>gildojiu</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6447,7 +6489,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>matheusteodoro_1</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6461,7 +6503,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6475,13 +6517,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>kael_lyto</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -6489,13 +6531,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ravenrodriguez___</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -6503,21 +6545,21 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D121">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>juanx.pontes</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6531,21 +6573,21 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>select_from_joao</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>yeslifeacademia</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6559,7 +6601,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ojaimerocha</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6573,13 +6615,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>tonketjudes</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -6587,13 +6629,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>_eliasffx</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -6601,7 +6643,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>pdfiv</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6615,7 +6657,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>mariaraimundad940</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6629,7 +6671,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>gabesantos.13</v>
+        <v>pdfiv</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6643,7 +6685,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>euvitormirandaa</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6657,7 +6699,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>thompsonborralho</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6671,7 +6713,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>frankikolimabjj</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6685,7 +6727,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6699,7 +6741,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6713,7 +6755,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>anahangelica</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6727,7 +6769,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6741,7 +6783,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>minotaurinho</v>
+        <v>anahangelica</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6755,7 +6797,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>lara.rpr</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6769,7 +6811,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>codasqueves</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6783,7 +6825,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>yan_touro.7766</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6797,7 +6839,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>carolinne.xwp</v>
+        <v>codasqueves</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -6811,7 +6853,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>davicorbella</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -6825,7 +6867,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -6839,7 +6881,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>davicorbella</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -6853,7 +6895,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>artemio_bjj</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -6867,7 +6909,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>katiaecarreraf</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -6881,7 +6923,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>geraldocnetomma</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -6895,7 +6937,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>xavyeroficial</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -6909,7 +6951,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>maryanagandra</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -6923,7 +6965,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>eliandropires</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -6937,7 +6979,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>charlesanthony2466</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -6951,7 +6993,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>eliandropires</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -6965,7 +7007,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>draanapaulaponceano</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -6979,7 +7021,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>saj_photo_miami</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -6993,7 +7035,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>alternativaremocoes</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7007,7 +7049,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>benivalentinn</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7021,7 +7063,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7035,7 +7077,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>navarro_9430</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7049,7 +7091,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>_puroosso88</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7063,7 +7105,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>_rayysp</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7077,7 +7119,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>cami.terra_</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7091,7 +7133,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>gabicardoson</v>
+        <v>_rayysp</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7105,7 +7147,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>martta.mariah</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7119,7 +7161,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>wlt_miguel</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7133,7 +7175,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7147,7 +7189,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>pietroshz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7161,7 +7203,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>___neller</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7175,7 +7217,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>_bety_marcal</v>
+        <v>pietroshz</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7189,7 +7231,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>guilhermeefelix__</v>
+        <v>___neller</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7203,7 +7245,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>pativinisf</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7217,7 +7259,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>judadany</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7231,7 +7273,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>andre_alcausa</v>
+        <v>pativinisf</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7245,7 +7287,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>_fernunes</v>
+        <v>judadany</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7259,7 +7301,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>aloirmarcal</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7273,7 +7315,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gilberto_7606</v>
+        <v>_fernunes</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7287,7 +7329,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7301,7 +7343,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>flazuera14</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7315,7 +7357,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7329,7 +7371,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7343,7 +7385,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>danlouiz.jj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7357,7 +7399,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>gabriel_trevelin</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7371,7 +7413,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>y.arthur_01</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7385,7 +7427,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>muricunha</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7399,7 +7441,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>victorhenriquebjj</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7413,7 +7455,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>_lsanchess_</v>
+        <v>muricunha</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7427,7 +7469,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>__bielgg</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7441,7 +7483,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mr__rlk01</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7455,7 +7497,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>vitor_buck</v>
+        <v>__bielgg</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7469,7 +7511,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>fran.ruys</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7483,7 +7525,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7497,7 +7539,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>wesley_bjjvc</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7511,7 +7553,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7525,7 +7567,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>peacegrappler</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7539,7 +7581,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>aliferpaulo_</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7553,7 +7595,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>jcchagas_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7567,7 +7609,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7581,7 +7623,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cesar.boanerges</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7595,7 +7637,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7609,7 +7651,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>alexandreconsentino</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7623,7 +7665,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7637,13 +7679,13 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>rafaela_duaartee</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -7651,7 +7693,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7665,13 +7707,13 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>andre.legendre.10</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -7679,7 +7721,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>phillipe.harry</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7693,7 +7735,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>andrejetx</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7707,7 +7749,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>leandro_motiv4</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7721,7 +7763,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>olga.oliveira013</v>
+        <v>andrejetx</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7735,7 +7777,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7749,7 +7791,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>leosacraa</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7763,7 +7805,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>gutocriativo</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7777,7 +7819,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>igorfso_</v>
+        <v>leosacraa</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7791,7 +7833,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7805,7 +7847,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>lay_roqs</v>
+        <v>igorfso_</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7819,7 +7861,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>bigjota.artist</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -7833,7 +7875,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -7847,7 +7889,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>mth_fernandes031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -7861,13 +7903,13 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>marinealcausa</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -7875,13 +7917,13 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>emersonriosmma</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -7889,27 +7931,27 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>luizcosta_mma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B220">
         <v>0</v>
       </c>
       <c r="C220">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>michelle_mirele</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B221">
         <v>0</v>
       </c>
       <c r="C221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -7917,49 +7959,49 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>danielfranzesilva</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B222">
         <v>0</v>
       </c>
       <c r="C222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ednilsonkaicai</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B223">
         <v>0</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D223">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>pedro_pavin_</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B224">
         <v>0</v>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -7973,7 +8015,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>dogodoyfoto</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -7982,18 +8024,18 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B227">
         <v>0</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -8001,21 +8043,21 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>leonardopateira</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
       <c r="C228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>rahikikhalid</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -8029,35 +8071,35 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>manumito.oficial</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>carlosnoelblack</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8071,63 +8113,63 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>lokomemo_protetores</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>coutz11</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>orlando_alfa09</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>vitorshowman</v>
+        <v>coutz11</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>4lissson</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8141,35 +8183,35 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>danilofernandescf</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>bryandazuera</v>
+        <v>4lissson</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8178,12 +8220,12 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>fredoctmma</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8192,12 +8234,12 @@
         <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8211,7 +8253,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>_kainanlima</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8225,7 +8267,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8239,7 +8281,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8253,7 +8295,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8267,7 +8309,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8281,7 +8323,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8295,7 +8337,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8309,7 +8351,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8323,7 +8365,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8337,7 +8379,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8351,7 +8393,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8365,7 +8407,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8379,7 +8421,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8393,7 +8435,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8407,7 +8449,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8421,7 +8463,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8435,7 +8477,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8449,7 +8491,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8463,7 +8505,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8477,7 +8519,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8491,7 +8533,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8505,7 +8547,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8519,7 +8561,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8533,7 +8575,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8547,7 +8589,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8561,7 +8603,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8575,7 +8617,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8589,7 +8631,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8603,7 +8645,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8617,7 +8659,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8631,7 +8673,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8645,7 +8687,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8659,7 +8701,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>ricardotofanello</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8673,7 +8715,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8687,7 +8729,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8701,7 +8743,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8715,7 +8757,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8729,7 +8771,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8743,7 +8785,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8757,7 +8799,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8771,7 +8813,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8785,7 +8827,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8799,7 +8841,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8813,7 +8855,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -8827,7 +8869,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -8841,7 +8883,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -8855,7 +8897,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -8869,7 +8911,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -8883,7 +8925,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -8897,7 +8939,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -8911,7 +8953,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -8925,7 +8967,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -8939,7 +8981,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -8953,7 +8995,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -8967,7 +9009,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -8981,7 +9023,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -8995,7 +9037,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9009,7 +9051,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9023,7 +9065,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9037,7 +9079,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9051,7 +9093,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9065,7 +9107,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9079,7 +9121,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9093,7 +9135,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9107,7 +9149,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9121,7 +9163,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9135,7 +9177,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9149,7 +9191,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9163,7 +9205,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9177,7 +9219,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9191,7 +9233,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9205,7 +9247,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9219,21 +9261,63 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
         <v>roginbrito</v>
       </c>
-      <c r="B315">
-        <v>0</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315">
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D315"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D318"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D320"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>472</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -601,13 +601,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -632,10 +632,10 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1004,111 +1004,111 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>karen.ottoni</v>
+        <v>paxlucta</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>_oliveira09_</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>fabinho_falcao_</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1116,24 +1116,24 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B54">
         <v>4</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>paxlucta</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1340,35 +1340,35 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>edebetim_</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>s__simone__</v>
+        <v>edebetim_</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1396,21 +1396,21 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -1424,41 +1424,41 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>marcos_tailandess</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>adriano.trator</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -1466,41 +1466,41 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>douglasipvr_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1508,13 +1508,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -1522,35 +1522,35 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -1564,16 +1564,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ismaeldaniell</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -1788,13 +1788,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>maca.mariotti</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -1802,21 +1802,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>treinaadorrafael</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -1844,13 +1844,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -1886,41 +1886,41 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>reifernandes</v>
+        <v>030sami</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>benjafloripabjj</v>
+        <v>reifernandes</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,13 +2082,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ravenrodriguez___</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -2110,35 +2110,35 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>cristianpsicologo</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,13 +2180,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>xavyeroficial</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>jcchagas_</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>_alcantara.bru</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,13 +3244,13 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -3258,13 +3258,13 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,13 +3468,13 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>marinealcausa</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C220">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -3496,35 +3496,35 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B222">
         <v>0</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>michelle_mirele</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B223">
         <v>0</v>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -3538,21 +3538,21 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B225">
         <v>0</v>
       </c>
       <c r="C225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>pedro_pavin_</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>dayanaa1511</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>dogodoyfoto</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -3589,26 +3589,26 @@
         <v>2</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>vanessamelomma</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -3636,21 +3636,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,21 +3678,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,21 +3706,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,21 +3748,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3785,12 +3785,12 @@
         <v>1</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>fredoctmma</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3799,12 +3799,12 @@
         <v>1</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>_kainanlima</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>ricardotofanello</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>roginbrito</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,28 +4840,56 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B318">
-        <v>0</v>
-      </c>
-      <c r="C318">
-        <v>1</v>
-      </c>
-      <c r="D318">
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D318"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D320"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D320"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4882,13 +4910,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>472</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3">
@@ -4896,13 +4924,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -4924,13 +4952,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -4952,7 +4980,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5064,13 +5092,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -5095,10 +5123,10 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -5467,111 +5495,111 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>karen.ottoni</v>
+        <v>paxlucta</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>_oliveira09_</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>fabinho_falcao_</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -5579,24 +5607,24 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5607,7 +5635,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B54">
         <v>4</v>
@@ -5621,13 +5649,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>paxlucta</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -5803,35 +5831,35 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>edebetim_</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>s__simone__</v>
+        <v>edebetim_</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -5845,7 +5873,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -5859,21 +5887,21 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -5887,41 +5915,41 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>marcos_tailandess</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>adriano.trator</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -5929,41 +5957,41 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>douglasipvr_mma</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -5971,13 +5999,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -5985,35 +6013,35 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -6027,16 +6055,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ismaeldaniell</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -6251,13 +6279,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>maca.mariotti</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -6265,21 +6293,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>treinaadorrafael</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6293,13 +6321,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6307,13 +6335,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6321,7 +6349,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6335,13 +6363,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6349,41 +6377,41 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>reifernandes</v>
+        <v>030sami</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>benjafloripabjj</v>
+        <v>reifernandes</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6391,7 +6419,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6405,7 +6433,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6419,7 +6447,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6433,7 +6461,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6447,7 +6475,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6461,7 +6489,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6475,7 +6503,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6489,7 +6517,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6503,7 +6531,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6517,7 +6545,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6531,7 +6559,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6545,13 +6573,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -6559,13 +6587,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ravenrodriguez___</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -6573,35 +6601,35 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>cristianpsicologo</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6615,7 +6643,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6629,7 +6657,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6643,13 +6671,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -6657,7 +6685,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6671,7 +6699,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6685,7 +6713,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6699,7 +6727,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6713,7 +6741,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6727,7 +6755,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6741,7 +6769,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6755,7 +6783,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6769,7 +6797,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6783,7 +6811,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6797,7 +6825,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6811,7 +6839,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6825,7 +6853,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6839,7 +6867,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -6853,7 +6881,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -6867,7 +6895,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -6881,7 +6909,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -6895,7 +6923,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -6909,7 +6937,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -6923,7 +6951,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -6937,7 +6965,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -6951,7 +6979,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -6965,7 +6993,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>xavyeroficial</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -6979,7 +7007,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -6993,7 +7021,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7007,7 +7035,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7021,7 +7049,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7035,7 +7063,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7049,7 +7077,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7063,7 +7091,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7077,7 +7105,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7091,7 +7119,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7105,7 +7133,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7119,7 +7147,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7133,7 +7161,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7147,7 +7175,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7161,7 +7189,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7175,7 +7203,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7189,7 +7217,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7203,7 +7231,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7217,7 +7245,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7231,7 +7259,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7245,7 +7273,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7259,7 +7287,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7273,7 +7301,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7287,7 +7315,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7301,7 +7329,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7315,7 +7343,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7329,7 +7357,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7343,7 +7371,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7357,7 +7385,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7371,7 +7399,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7385,7 +7413,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7399,7 +7427,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7413,7 +7441,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7427,7 +7455,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7441,7 +7469,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7455,7 +7483,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7469,7 +7497,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7483,7 +7511,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7497,7 +7525,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7511,7 +7539,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7525,7 +7553,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7539,7 +7567,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7553,7 +7581,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7567,7 +7595,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7581,7 +7609,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7595,7 +7623,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7609,7 +7637,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7623,7 +7651,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>jcchagas_</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7637,7 +7665,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>_alcantara.bru</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7651,7 +7679,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7665,7 +7693,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7679,7 +7707,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7693,7 +7721,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7707,13 +7735,13 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -7721,13 +7749,13 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -7735,7 +7763,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7749,7 +7777,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7763,7 +7791,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7777,7 +7805,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7791,7 +7819,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7805,7 +7833,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7819,7 +7847,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7833,7 +7861,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7847,7 +7875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7861,7 +7889,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -7875,7 +7903,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -7889,7 +7917,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -7903,7 +7931,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -7917,7 +7945,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -7931,13 +7959,13 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>marinealcausa</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C220">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -7945,7 +7973,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -7959,35 +7987,35 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B222">
         <v>0</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>michelle_mirele</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B223">
         <v>0</v>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -8001,21 +8029,21 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B225">
         <v>0</v>
       </c>
       <c r="C225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>pedro_pavin_</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -8029,7 +8057,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>dayanaa1511</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -8043,7 +8071,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>dogodoyfoto</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -8052,26 +8080,26 @@
         <v>2</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>vanessamelomma</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -8085,7 +8113,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -8099,21 +8127,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8127,7 +8155,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8141,21 +8169,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8169,21 +8197,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8197,7 +8225,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8211,21 +8239,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8239,7 +8267,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8248,12 +8276,12 @@
         <v>1</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>fredoctmma</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8262,12 +8290,12 @@
         <v>1</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8281,7 +8309,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>_kainanlima</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8295,7 +8323,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8309,7 +8337,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8323,7 +8351,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8337,7 +8365,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8351,7 +8379,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8365,7 +8393,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8379,7 +8407,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8393,7 +8421,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8407,7 +8435,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8421,7 +8449,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8435,7 +8463,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8449,7 +8477,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8463,7 +8491,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8477,7 +8505,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8491,7 +8519,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8505,7 +8533,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8519,7 +8547,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8533,7 +8561,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8547,7 +8575,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8561,7 +8589,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8575,7 +8603,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8589,7 +8617,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8603,7 +8631,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8617,7 +8645,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8631,7 +8659,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8645,7 +8673,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8659,7 +8687,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8673,7 +8701,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8687,7 +8715,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8701,7 +8729,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8715,7 +8743,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8729,7 +8757,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>ricardotofanello</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8743,7 +8771,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8757,7 +8785,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8771,7 +8799,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8785,7 +8813,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8799,7 +8827,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8813,7 +8841,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8827,7 +8855,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8841,7 +8869,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8855,7 +8883,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -8869,7 +8897,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -8883,7 +8911,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -8897,7 +8925,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -8911,7 +8939,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -8925,7 +8953,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -8939,7 +8967,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -8953,7 +8981,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -8967,7 +8995,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -8981,7 +9009,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -8995,7 +9023,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9009,7 +9037,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9023,7 +9051,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9037,7 +9065,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9051,7 +9079,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9065,7 +9093,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9079,7 +9107,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9093,7 +9121,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9107,7 +9135,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9121,7 +9149,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9135,7 +9163,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9149,7 +9177,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9163,7 +9191,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9177,7 +9205,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9191,7 +9219,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9205,7 +9233,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9219,7 +9247,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9233,7 +9261,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9247,7 +9275,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9261,7 +9289,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9275,7 +9303,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9289,7 +9317,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>roginbrito</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9303,21 +9331,49 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B318">
-        <v>0</v>
-      </c>
-      <c r="C318">
-        <v>1</v>
-      </c>
-      <c r="D318">
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D318"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D320"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -730,10 +730,10 @@
         <v>11</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -906,30 +906,30 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gdazuera</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4994,13 +4994,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -5221,10 +5221,10 @@
         <v>11</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -5397,30 +5397,30 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gdazuera</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D320"/>
+  <dimension ref="A1:D322"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>488</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -604,10 +604,10 @@
         <v>28</v>
       </c>
       <c r="C15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -632,10 +632,10 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -752,41 +752,41 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>eliassilverio</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B26">
         <v>8</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>tawanregismma</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -794,13 +794,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tabajaraharu</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -808,16 +808,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>cleyton_jesuss</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1060,13 +1060,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1074,55 +1074,55 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>fabinho_falcao_</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1130,24 +1130,24 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -1172,21 +1172,21 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>shawlin13oficial</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -1214,35 +1214,35 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>marcelogabrielmma</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -1256,27 +1256,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -1284,41 +1284,41 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>anderson.logan.35</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>marifferreirac</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1326,77 +1326,77 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>odeivisoncardoso</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>marcos_tailandess</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>edebetim_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>s__simone__</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>kaua_limaofc</v>
+        <v>edebetim_</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>clouddhidden</v>
+        <v>s__simone__</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -1410,97 +1410,97 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lucascardosol__</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ruangzk</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>washington_cassisno</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>adriano.trator</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>tassiogiloficial</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1508,21 +1508,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,63 +1536,63 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>diegopaivajj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fabaotipster</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -1601,54 +1601,54 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>joegam3r</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>mimuniz.bjj</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>orafao1</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabi.godooy</v>
+        <v>joegam3r</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -1662,49 +1662,49 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>leobahiamma</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>orafao1</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>heltoncm2002</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>raelduraes</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>mineirinho_jj</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>graalino</v>
+        <v>raelduraes</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>badboykillermma</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>lopesbrunao</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,13 +1802,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>maca.mariotti</v>
+        <v>graalino</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -1816,55 +1816,55 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>treinaadorrafael</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fernando.mma</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fagnerosensei</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -1886,13 +1886,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>030sami</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -1900,21 +1900,21 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>benjafloripabjj</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>guiiviieira_</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>cshigueo</v>
+        <v>030sami</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>emerson_lucaszx</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>danni_goncalves12</v>
+        <v>cshigueo</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>mttsm._</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>andrealvess02</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>gildojiu</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>kawannsennast</v>
+        <v>mttsm._</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>yurimartins1_</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>matheusteodoro_1</v>
+        <v>gildojiu</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>kael_lyto</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>ravenrodriguez___</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -2124,27 +2124,27 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>cristianpsicologo</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>juanx.pontes</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>select_from_joao</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,21 +2166,21 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>yeslifeacademia</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ojaimerocha</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,13 +2194,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>tonketjudes</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -2208,13 +2208,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>_eliasffx</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -2222,13 +2222,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>pdfiv</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>mariaraimundad940</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>gabesantos.13</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>euvitormirandaa</v>
+        <v>pdfiv</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>thompsonborralho</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>frankikolimabjj</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>alerrandrojj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>anahangelica</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>minotaurinho</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>lara.rpr</v>
+        <v>anahangelica</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>codasqueves</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>yan_touro.7766</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>carolinne.xwp</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>davicorbella</v>
+        <v>codasqueves</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>artemio_bjj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>katiaecarreraf</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>geraldocnetomma</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>xavyeroficial</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>maryanagandra</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>eliandropires</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,21 +2558,21 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>charlesanthony2466</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>draanapaulaponceano</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>saj_photo_miami</v>
+        <v>eliandropires</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>alternativaremocoes</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>benivalentinn</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>navarro_9430</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>_puroosso88</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>_rayysp</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>cami.terra_</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>gabicardoson</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>martta.mariah</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>wlt_miguel</v>
+        <v>_rayysp</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>jaonevesz</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>pietroshz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>___neller</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>_bety_marcal</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>guilhermeefelix__</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>pativinisf</v>
+        <v>pietroshz</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>judadany</v>
+        <v>___neller</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>andre_alcausa</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>_fernunes</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>aloirmarcal</v>
+        <v>pativinisf</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>gilberto_7606</v>
+        <v>judadany</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>flazuera14</v>
+        <v>_fernunes</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>camii_bonfim</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>danlouiz.jj</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gabriel_trevelin</v>
+        <v>flazuera14</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>y.arthur_01</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>muricunha</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>victorhenriquebjj</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>_lsanchess_</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>__bielgg</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>mr__rlk01</v>
+        <v>muricunha</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>vitor_buck</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>fran.ruys</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>__bielgg</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>wesley_bjjvc</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>sambagabrieloficial</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>peacegrappler</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>aliferpaulo_</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>jcchagas_</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cesar.boanerges</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>alexandreconsentino</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,13 +3258,13 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>andre.legendre.10</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>phillipe.harry</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>andrejetx</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>leandro_motiv4</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>olga.oliveira013</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>andrejetx</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>leosacraa</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>gutocriativo</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>igorfso_</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>leosacraa</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>lay_roqs</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>bigjota.artist</v>
+        <v>igorfso_</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>mth_fernandes031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,13 +3482,13 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>marinealcausa</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C221">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -3496,13 +3496,13 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>emersonriosmma</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -3510,27 +3510,27 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>luizcosta_mma</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>michelle_mirele</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -3538,13 +3538,13 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>danielfranzesilva</v>
+        <v>turmanmma</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -3552,35 +3552,35 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>ednilsonkaicai</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B226">
         <v>0</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>pedro_pavin_</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B227">
         <v>0</v>
       </c>
       <c r="C227">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>dayanaa1511</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -3589,18 +3589,18 @@
         <v>2</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>dogodoyfoto</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -3608,27 +3608,27 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>vanessamelomma</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>leonardopateira</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -3636,13 +3636,13 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>rahikikhalid</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -3650,77 +3650,77 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>manumito.oficial</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>carlosnoelblack</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>lokomemo_protetores</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>coutz11</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>orlando_alfa09</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,77 +3734,77 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>vitorshowman</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>4lissson</v>
+        <v>coutz11</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>danilofernandescf</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>bryandazuera</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>giulia.fasolato</v>
+        <v>4lissson</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3813,12 +3813,12 @@
         <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>fredoctmma</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3827,12 +3827,12 @@
         <v>1</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>helenaseveribjj</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3841,12 +3841,12 @@
         <v>1</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>_kainanlima</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>ricardotofanello</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>roginbrito</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,28 +4868,56 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B320">
-        <v>0</v>
-      </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320">
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D322"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D320"/>
+  <dimension ref="A1:D322"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4910,13 +4938,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>488</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3">
@@ -4924,13 +4952,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
@@ -4994,7 +5022,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -5095,10 +5123,10 @@
         <v>28</v>
       </c>
       <c r="C15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -5123,10 +5151,10 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -5243,41 +5271,41 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>eliassilverio</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B26">
         <v>8</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>tawanregismma</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -5285,13 +5313,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tabajaraharu</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -5299,16 +5327,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>cleyton_jesuss</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -5551,13 +5579,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -5565,55 +5593,55 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>fabinho_falcao_</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -5621,24 +5649,24 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5649,7 +5677,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -5663,21 +5691,21 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>shawlin13oficial</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -5691,7 +5719,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -5705,35 +5733,35 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>marcelogabrielmma</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -5747,27 +5775,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -5775,41 +5803,41 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>anderson.logan.35</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>marifferreirac</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -5817,77 +5845,77 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>odeivisoncardoso</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>marcos_tailandess</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>edebetim_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>s__simone__</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>kaua_limaofc</v>
+        <v>edebetim_</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>clouddhidden</v>
+        <v>s__simone__</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -5901,97 +5929,97 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lucascardosol__</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>ruangzk</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>washington_cassisno</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>adriano.trator</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>tassiogiloficial</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -5999,21 +6027,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -6027,63 +6055,63 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>diegopaivajj</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fabaotipster</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -6092,54 +6120,54 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>joegam3r</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>mimuniz.bjj</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>orafao1</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabi.godooy</v>
+        <v>joegam3r</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -6153,49 +6181,49 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>leobahiamma</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>orafao1</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>heltoncm2002</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -6209,7 +6237,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>raelduraes</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -6223,7 +6251,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -6237,7 +6265,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>mineirinho_jj</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -6251,7 +6279,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>graalino</v>
+        <v>raelduraes</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6265,7 +6293,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>badboykillermma</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6279,7 +6307,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>lopesbrunao</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6293,13 +6321,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>maca.mariotti</v>
+        <v>graalino</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -6307,55 +6335,55 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>treinaadorrafael</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fernando.mma</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -6363,13 +6391,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fagnerosensei</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6377,13 +6405,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>030sami</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6391,21 +6419,21 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>benjafloripabjj</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6419,13 +6447,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>guiiviieira_</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6433,7 +6461,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>cshigueo</v>
+        <v>030sami</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6447,13 +6475,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -6461,7 +6489,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>emerson_lucaszx</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6475,7 +6503,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>danni_goncalves12</v>
+        <v>cshigueo</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6489,7 +6517,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>mttsm._</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6503,7 +6531,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>andrealvess02</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6517,7 +6545,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>gildojiu</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6531,7 +6559,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>kawannsennast</v>
+        <v>mttsm._</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6545,7 +6573,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>yurimartins1_</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6559,7 +6587,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>matheusteodoro_1</v>
+        <v>gildojiu</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6573,7 +6601,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6587,13 +6615,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>kael_lyto</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -6601,13 +6629,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>ravenrodriguez___</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -6615,27 +6643,27 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>cristianpsicologo</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>juanx.pontes</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -6643,7 +6671,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>select_from_joao</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6657,21 +6685,21 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>yeslifeacademia</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>ojaimerocha</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6685,13 +6713,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>tonketjudes</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -6699,13 +6727,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>_eliasffx</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -6713,13 +6741,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>pdfiv</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -6727,7 +6755,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>mariaraimundad940</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6741,7 +6769,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>gabesantos.13</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6755,7 +6783,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>euvitormirandaa</v>
+        <v>pdfiv</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6769,7 +6797,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>thompsonborralho</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6783,7 +6811,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>frankikolimabjj</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6797,7 +6825,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6811,7 +6839,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>alerrandrojj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6825,7 +6853,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>anahangelica</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6839,7 +6867,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6853,7 +6881,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>minotaurinho</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6867,7 +6895,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>lara.rpr</v>
+        <v>anahangelica</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -6881,7 +6909,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>codasqueves</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -6895,7 +6923,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>yan_touro.7766</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -6909,7 +6937,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>carolinne.xwp</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -6923,7 +6951,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>davicorbella</v>
+        <v>codasqueves</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -6937,7 +6965,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -6951,7 +6979,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -6965,7 +6993,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>artemio_bjj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -6979,7 +7007,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>katiaecarreraf</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -6993,7 +7021,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>geraldocnetomma</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7007,7 +7035,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>xavyeroficial</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7021,7 +7049,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>maryanagandra</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7035,7 +7063,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>eliandropires</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7049,21 +7077,21 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>charlesanthony2466</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7077,7 +7105,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>draanapaulaponceano</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7091,7 +7119,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>saj_photo_miami</v>
+        <v>eliandropires</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7105,7 +7133,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>alternativaremocoes</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7119,7 +7147,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>benivalentinn</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7133,7 +7161,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7147,7 +7175,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>navarro_9430</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7161,7 +7189,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>_puroosso88</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7175,7 +7203,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>_rayysp</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7189,7 +7217,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>cami.terra_</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7203,7 +7231,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>gabicardoson</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7217,7 +7245,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>martta.mariah</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7231,7 +7259,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>wlt_miguel</v>
+        <v>_rayysp</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7245,7 +7273,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>jaonevesz</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7259,7 +7287,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>pietroshz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7273,7 +7301,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>___neller</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7287,7 +7315,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>_bety_marcal</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7301,7 +7329,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>guilhermeefelix__</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7315,7 +7343,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>pativinisf</v>
+        <v>pietroshz</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7329,7 +7357,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>judadany</v>
+        <v>___neller</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7343,7 +7371,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>andre_alcausa</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7357,7 +7385,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>_fernunes</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7371,7 +7399,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>aloirmarcal</v>
+        <v>pativinisf</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7385,7 +7413,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>gilberto_7606</v>
+        <v>judadany</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7399,7 +7427,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7413,7 +7441,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>flazuera14</v>
+        <v>_fernunes</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7427,7 +7455,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7441,7 +7469,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>camii_bonfim</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7455,7 +7483,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>danlouiz.jj</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7469,7 +7497,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gabriel_trevelin</v>
+        <v>flazuera14</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7483,7 +7511,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>y.arthur_01</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7497,7 +7525,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>muricunha</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7511,7 +7539,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>victorhenriquebjj</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7525,7 +7553,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>_lsanchess_</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7539,7 +7567,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>__bielgg</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7553,7 +7581,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>mr__rlk01</v>
+        <v>muricunha</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7567,7 +7595,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>vitor_buck</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7581,7 +7609,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>fran.ruys</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7595,7 +7623,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>__bielgg</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7609,7 +7637,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>wesley_bjjvc</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7623,7 +7651,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>sambagabrieloficial</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7637,7 +7665,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>peacegrappler</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7651,7 +7679,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>aliferpaulo_</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7665,7 +7693,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>jcchagas_</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7679,7 +7707,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7693,7 +7721,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cesar.boanerges</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7707,7 +7735,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7721,7 +7749,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>alexandreconsentino</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7735,7 +7763,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7749,13 +7777,13 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -7763,7 +7791,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7777,7 +7805,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>andre.legendre.10</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7791,13 +7819,13 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>phillipe.harry</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -7805,7 +7833,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>andrejetx</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7819,7 +7847,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>leandro_motiv4</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7833,7 +7861,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>olga.oliveira013</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7847,7 +7875,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>andrejetx</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7861,7 +7889,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>leosacraa</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7875,7 +7903,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>gutocriativo</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7889,7 +7917,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>igorfso_</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -7903,7 +7931,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>leosacraa</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -7917,7 +7945,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>lay_roqs</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -7931,7 +7959,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>bigjota.artist</v>
+        <v>igorfso_</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -7945,7 +7973,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -7959,7 +7987,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>mth_fernandes031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -7973,13 +8001,13 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>marinealcausa</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C221">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -7987,13 +8015,13 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>emersonriosmma</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -8001,27 +8029,27 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>luizcosta_mma</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>michelle_mirele</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -8029,13 +8057,13 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>danielfranzesilva</v>
+        <v>turmanmma</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -8043,35 +8071,35 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>ednilsonkaicai</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B226">
         <v>0</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>pedro_pavin_</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B227">
         <v>0</v>
       </c>
       <c r="C227">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>dayanaa1511</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -8080,18 +8108,18 @@
         <v>2</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>dogodoyfoto</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -8099,27 +8127,27 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>vanessamelomma</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>leonardopateira</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -8127,13 +8155,13 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>rahikikhalid</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -8141,77 +8169,77 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>manumito.oficial</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>carlosnoelblack</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>lokomemo_protetores</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>coutz11</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>orlando_alfa09</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8225,77 +8253,77 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>vitorshowman</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>4lissson</v>
+        <v>coutz11</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>danilofernandescf</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>bryandazuera</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>giulia.fasolato</v>
+        <v>4lissson</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8304,12 +8332,12 @@
         <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>fredoctmma</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8318,12 +8346,12 @@
         <v>1</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>helenaseveribjj</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8332,12 +8360,12 @@
         <v>1</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>_kainanlima</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8351,7 +8379,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8365,7 +8393,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8379,7 +8407,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8393,7 +8421,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8407,7 +8435,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8421,7 +8449,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8435,7 +8463,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8449,7 +8477,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8463,7 +8491,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8477,7 +8505,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8491,7 +8519,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8505,7 +8533,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8519,7 +8547,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8533,7 +8561,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8547,7 +8575,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8561,7 +8589,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8575,7 +8603,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8589,7 +8617,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8603,7 +8631,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8617,7 +8645,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8631,7 +8659,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8645,7 +8673,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8659,7 +8687,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8673,7 +8701,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8687,7 +8715,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8701,7 +8729,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8715,7 +8743,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8729,7 +8757,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8743,7 +8771,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8757,7 +8785,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8771,7 +8799,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8785,7 +8813,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>ricardotofanello</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8799,7 +8827,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8813,7 +8841,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8827,7 +8855,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8841,7 +8869,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8855,7 +8883,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8869,7 +8897,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8883,7 +8911,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -8897,7 +8925,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -8911,7 +8939,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -8925,7 +8953,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -8939,7 +8967,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -8953,7 +8981,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -8967,7 +8995,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -8981,7 +9009,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -8995,7 +9023,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9009,7 +9037,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9023,7 +9051,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9037,7 +9065,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9051,7 +9079,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9065,7 +9093,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9079,7 +9107,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9093,7 +9121,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9107,7 +9135,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9121,7 +9149,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9135,7 +9163,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9149,7 +9177,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9163,7 +9191,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9177,7 +9205,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9191,7 +9219,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9205,7 +9233,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9219,7 +9247,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9233,7 +9261,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9247,7 +9275,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9261,7 +9289,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9275,7 +9303,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9289,7 +9317,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9303,7 +9331,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9317,7 +9345,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9331,7 +9359,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9345,7 +9373,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>roginbrito</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9359,21 +9387,49 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B320">
-        <v>0</v>
-      </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320">
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D322"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D325"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>503</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -654,44 +654,44 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>gra_jpereira</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>combintel</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mmmarc20</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -741,38 +741,38 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>cleyton_jesuss</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>pedromadeira.s</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -822,128 +822,128 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>rrafaelins</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>italothearcher</v>
       </c>
       <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="D34">
         <v>6</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>vndcardoso</v>
+        <v>maxgandra</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gdazuera</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>rm.nicki</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1228,35 +1228,35 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1270,83 +1270,83 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>f.luan_11</v>
+        <v>edebetim_</v>
       </c>
       <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
         <v>3</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
       <c r="D64">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>vitorpetrino</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>jcchagas_</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>anderson.logan.35</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>marifferreirac</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -1354,77 +1354,77 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>odeivisoncardoso</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marcos_tailandess</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>edebetim_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>s__simone__</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>kaua_limaofc</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>clouddhidden</v>
+        <v>s__simone__</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -1438,111 +1438,111 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lucascardosol__</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ruangzk</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>washington_cassisno</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>adriano.trator</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -1550,13 +1550,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -1564,35 +1564,35 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -1615,18 +1615,18 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -1648,35 +1648,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>mimuniz.bjj</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>orafao1</v>
+        <v>joegam3r</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fabi.godooy</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -1704,35 +1704,35 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>leobahiamma</v>
+        <v>orafao1</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>heltoncm2002</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>raelduraes</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mineirinho_jj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>graalino</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>badboykillermma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,13 +1844,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>maca.mariotti</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -1858,41 +1858,41 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fernando.mma</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -1900,13 +1900,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>dogodoyfoto</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -1914,13 +1914,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,13 +1942,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2152,13 +2152,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ravenrodriguez___</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -2166,35 +2166,35 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>cristianpsicologo</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,35 +2558,35 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -3314,13 +3314,13 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,13 +3552,13 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -3580,35 +3580,35 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
       <c r="C228">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D228">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>michelle_mirele</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -3622,21 +3622,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -3650,13 +3650,13 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -3692,21 +3692,21 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,21 +3734,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,21 +3762,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,21 +3804,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>giulia.fasolato</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3855,12 +3855,12 @@
         <v>1</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>helenaseveribjj</v>
+        <v>ommariotti</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3869,12 +3869,12 @@
         <v>1</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>_kainanlima</v>
+        <v>brodschack_</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3883,12 +3883,12 @@
         <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>jimmy_indioap</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>omar_alneaimi</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>victor_brunopersonal</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>motumbo_team</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>vanemessina</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>dadwillians</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>thalytabjj</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>vanemessina</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>chubotaru_lilu</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>eusoufernandosaito</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>dandraco_</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>sejamotivadorofc</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>tpapereira</v>
+        <v>dandraco_</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>kfcampeoes</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>herrickmarinho</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>rafaelcmjj</v>
+        <v>tpapereira</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>cristianomarcello</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>_gabrielpego</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>taylor_71kg</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>doraasivla</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>pe.mirandas</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>leaoanaalice</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>caioparangole</v>
+        <v>doraasivla</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>sabrinaalsilva</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>eglaudiomma</v>
+        <v>caioparangole</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>strong_stg_oficial</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ricardotofanello</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>taporondebruno</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>anamatias.m</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>claudio_marchese_7</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>1000ton_n</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>paulo.titoo</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>vitorcosta_mma</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>couragemma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>romulerasilva</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>edergama.mma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>alineanne_</v>
+        <v>couragemma</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>julckreis</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>andreza.thais.1</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>benicius_edu</v>
+        <v>alineanne_</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>julckreis</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>michele_mixa</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>joaolauar_</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>igorbrasileiro01</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>felipeocalmon</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>rejr_mma</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>deivssonmanin</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>andrey_m_s_</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>vidaldanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>barbaracontadora</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>natalves5</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>boradepodcastoficial</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>audizioandrade</v>
+        <v>natalves5</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>isadoragolimpio</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>dudu.acabamentos</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>katlembrenda</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>aline.amaral21</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>tamysregina</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>guilhermews1994</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>percepcar</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>kevin.mota95</v>
+        <v>tamysregina</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>_marcos_.71</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>douglas_vitor8</v>
+        <v>percepcar</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>raulcarvalho1010</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>roginbrito</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,28 +4896,70 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B322">
-        <v>0</v>
-      </c>
-      <c r="C322">
-        <v>1</v>
-      </c>
-      <c r="D322">
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+      <c r="D325">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D322"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D325"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D322"/>
+  <dimension ref="A1:D325"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4938,13 +4980,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>503</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3">
@@ -4952,13 +4994,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
@@ -4994,13 +5036,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -5036,13 +5078,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -5120,13 +5162,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -5173,44 +5215,44 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>gra_jpereira</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>combintel</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mmmarc20</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -5260,38 +5302,38 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>cleyton_jesuss</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -5299,13 +5341,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>pedromadeira.s</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -5341,128 +5383,128 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>rrafaelins</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>italothearcher</v>
       </c>
       <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="D34">
         <v>6</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>vndcardoso</v>
+        <v>maxgandra</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gdazuera</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>rm.nicki</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -5747,35 +5789,35 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -5789,83 +5831,83 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>f.luan_11</v>
+        <v>edebetim_</v>
       </c>
       <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
         <v>3</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
       <c r="D64">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>vitorpetrino</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>jcchagas_</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>anderson.logan.35</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>marifferreirac</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -5873,77 +5915,77 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>odeivisoncardoso</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marcos_tailandess</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>edebetim_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>s__simone__</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>kaua_limaofc</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>clouddhidden</v>
+        <v>s__simone__</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -5957,111 +5999,111 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lucascardosol__</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>ruangzk</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>washington_cassisno</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>adriano.trator</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -6069,13 +6111,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -6083,35 +6125,35 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -6125,7 +6167,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -6134,18 +6176,18 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -6153,13 +6195,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -6167,35 +6209,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>mimuniz.bjj</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>orafao1</v>
+        <v>joegam3r</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -6209,7 +6251,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fabi.godooy</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -6223,35 +6265,35 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>leobahiamma</v>
+        <v>orafao1</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -6265,7 +6307,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>heltoncm2002</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -6279,7 +6321,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>raelduraes</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6293,7 +6335,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6307,7 +6349,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mineirinho_jj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6321,7 +6363,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>graalino</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6335,7 +6377,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>badboykillermma</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6349,7 +6391,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6363,13 +6405,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>maca.mariotti</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -6377,41 +6419,41 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fernando.mma</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6419,13 +6461,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>dogodoyfoto</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6433,13 +6475,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6447,7 +6489,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6461,13 +6503,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -6475,13 +6517,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -6489,13 +6531,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6503,7 +6545,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6517,7 +6559,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6531,7 +6573,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6545,7 +6587,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6559,7 +6601,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6573,7 +6615,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6587,7 +6629,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6601,7 +6643,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6615,7 +6657,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6629,7 +6671,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6643,7 +6685,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6657,13 +6699,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -6671,13 +6713,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ravenrodriguez___</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -6685,35 +6727,35 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>cristianpsicologo</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6727,7 +6769,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6741,7 +6783,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6755,13 +6797,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -6769,7 +6811,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6783,7 +6825,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6797,7 +6839,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6811,7 +6853,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6825,7 +6867,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6839,7 +6881,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6853,7 +6895,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6867,7 +6909,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6881,7 +6923,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6895,7 +6937,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -6909,7 +6951,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -6923,7 +6965,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -6937,7 +6979,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -6951,7 +6993,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -6965,7 +7007,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -6979,7 +7021,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -6993,7 +7035,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7007,7 +7049,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7021,7 +7063,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7035,7 +7077,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7049,7 +7091,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7063,7 +7105,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7077,35 +7119,35 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7119,7 +7161,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7133,7 +7175,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7147,7 +7189,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7161,7 +7203,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7175,7 +7217,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7189,7 +7231,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7203,7 +7245,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7217,7 +7259,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7231,7 +7273,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7245,7 +7287,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7259,7 +7301,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7273,7 +7315,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7287,7 +7329,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7301,7 +7343,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7315,7 +7357,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7329,7 +7371,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7343,7 +7385,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7357,7 +7399,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7371,7 +7413,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7385,7 +7427,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7399,7 +7441,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7413,7 +7455,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7427,7 +7469,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7441,7 +7483,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7455,7 +7497,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7469,7 +7511,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7483,7 +7525,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7497,7 +7539,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7511,7 +7553,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7525,7 +7567,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7539,7 +7581,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7553,7 +7595,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7567,7 +7609,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7581,7 +7623,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7595,7 +7637,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7609,7 +7651,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7623,7 +7665,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7637,7 +7679,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7651,7 +7693,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7665,7 +7707,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7679,7 +7721,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7693,7 +7735,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7707,7 +7749,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7721,7 +7763,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7735,7 +7777,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7749,7 +7791,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7763,7 +7805,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7777,7 +7819,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7791,7 +7833,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7805,7 +7847,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7819,13 +7861,13 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -7833,13 +7875,13 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -7847,7 +7889,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7861,7 +7903,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7875,7 +7917,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7889,7 +7931,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7903,7 +7945,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7917,7 +7959,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -7931,7 +7973,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -7945,7 +7987,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -7959,7 +8001,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -7973,7 +8015,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -7987,7 +8029,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8001,7 +8043,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8015,7 +8057,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8029,7 +8071,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8043,7 +8085,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8057,7 +8099,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8071,13 +8113,13 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -8085,7 +8127,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -8099,35 +8141,35 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
       <c r="C228">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D228">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>michelle_mirele</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -8141,21 +8183,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8169,13 +8211,13 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -8183,7 +8225,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8197,7 +8239,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8211,21 +8253,21 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8239,7 +8281,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8253,21 +8295,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8281,21 +8323,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8309,7 +8351,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8323,21 +8365,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8351,7 +8393,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>giulia.fasolato</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8365,7 +8407,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8374,12 +8416,12 @@
         <v>1</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>helenaseveribjj</v>
+        <v>ommariotti</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8388,12 +8430,12 @@
         <v>1</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>_kainanlima</v>
+        <v>brodschack_</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8402,12 +8444,12 @@
         <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>jimmy_indioap</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8421,7 +8463,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>omar_alneaimi</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8435,7 +8477,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>victor_brunopersonal</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8449,7 +8491,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>motumbo_team</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8463,7 +8505,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>vanemessina</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8477,7 +8519,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>dadwillians</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8491,7 +8533,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>thalytabjj</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8505,7 +8547,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>vanemessina</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8519,7 +8561,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8533,7 +8575,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>chubotaru_lilu</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8547,7 +8589,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>eusoufernandosaito</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8561,7 +8603,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>dandraco_</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8575,7 +8617,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8589,7 +8631,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>sejamotivadorofc</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8603,7 +8645,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>tpapereira</v>
+        <v>dandraco_</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8617,7 +8659,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>kfcampeoes</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8631,7 +8673,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>herrickmarinho</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8645,7 +8687,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>rafaelcmjj</v>
+        <v>tpapereira</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8659,7 +8701,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>cristianomarcello</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8673,7 +8715,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>_gabrielpego</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8687,7 +8729,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>taylor_71kg</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8701,7 +8743,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8715,7 +8757,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>doraasivla</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8729,7 +8771,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>pe.mirandas</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8743,7 +8785,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>leaoanaalice</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8757,7 +8799,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>caioparangole</v>
+        <v>doraasivla</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8771,7 +8813,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>sabrinaalsilva</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8785,7 +8827,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8799,7 +8841,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>eglaudiomma</v>
+        <v>caioparangole</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8813,7 +8855,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8827,7 +8869,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>strong_stg_oficial</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8841,7 +8883,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ricardotofanello</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8855,7 +8897,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>taporondebruno</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8869,7 +8911,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>anamatias.m</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8883,7 +8925,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>claudio_marchese_7</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8897,7 +8939,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>1000ton_n</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8911,7 +8953,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>paulo.titoo</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -8925,7 +8967,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>vitorcosta_mma</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -8939,7 +8981,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>couragemma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -8953,7 +8995,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>romulerasilva</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -8967,7 +9009,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>edergama.mma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -8981,7 +9023,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>alineanne_</v>
+        <v>couragemma</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -8995,7 +9037,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>julckreis</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9009,7 +9051,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>andreza.thais.1</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9023,7 +9065,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>benicius_edu</v>
+        <v>alineanne_</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9037,7 +9079,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>julckreis</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9051,7 +9093,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>michele_mixa</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9065,7 +9107,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>joaolauar_</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9079,7 +9121,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>igorbrasileiro01</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9093,7 +9135,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>felipeocalmon</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9107,7 +9149,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>rejr_mma</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9121,7 +9163,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>deivssonmanin</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9135,7 +9177,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>andrey_m_s_</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9149,7 +9191,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>vidaldanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9163,7 +9205,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>barbaracontadora</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9177,7 +9219,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>natalves5</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9191,7 +9233,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9205,7 +9247,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>boradepodcastoficial</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9219,7 +9261,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>audizioandrade</v>
+        <v>natalves5</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9233,7 +9275,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>isadoragolimpio</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9247,7 +9289,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>dudu.acabamentos</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9261,7 +9303,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>katlembrenda</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9275,7 +9317,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>aline.amaral21</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9289,7 +9331,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>tamysregina</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9303,7 +9345,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>guilhermews1994</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9317,7 +9359,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>percepcar</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9331,7 +9373,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>kevin.mota95</v>
+        <v>tamysregina</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9345,7 +9387,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>_marcos_.71</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9359,7 +9401,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>douglas_vitor8</v>
+        <v>percepcar</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9373,7 +9415,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9387,7 +9429,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>raulcarvalho1010</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9401,7 +9443,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>roginbrito</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9415,21 +9457,63 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B322">
-        <v>0</v>
-      </c>
-      <c r="C322">
-        <v>1</v>
-      </c>
-      <c r="D322">
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+      <c r="D325">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D322"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D325"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D327"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3">
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -626,30 +626,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>god.motivacao</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>leandro._bjj</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -657,24 +657,24 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mmmarc20</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -724,30 +724,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>anaaj_camargo</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -794,27 +794,27 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tawanregismma</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tabajaraharu</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -1242,35 +1242,35 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>reifernandes</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1284,41 +1284,41 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -1326,21 +1326,21 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1354,55 +1354,55 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -1410,35 +1410,35 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1466,21 +1466,21 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -1494,69 +1494,69 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -1578,35 +1578,35 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -1629,18 +1629,18 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -1648,13 +1648,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -1662,35 +1662,35 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>maca.mariotti</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>joegam3r</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1732,21 +1732,21 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>badboykillermma</v>
+        <v>graalino</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>lopesbrunao</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>cjrnavalha</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,21 +1886,21 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>treinaadorrafael</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,13 +1914,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,13 +2152,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ravenrodriguez___</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -3664,13 +3664,13 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,21 +3706,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,21 +3748,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,21 +3776,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,21 +3818,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>giulia.fasolato</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ommariotti</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>brodschack_</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3897,12 +3897,12 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>helenaseveribjj</v>
+        <v>_vpft</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3911,12 +3911,12 @@
         <v>1</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>_kainanlima</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,28 +4938,56 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B325">
-        <v>0</v>
-      </c>
-      <c r="C325">
-        <v>1</v>
-      </c>
-      <c r="D325">
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D325"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D327"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D327"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4980,13 +5008,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3">
@@ -5008,13 +5036,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -5036,13 +5064,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -5078,13 +5106,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -5187,30 +5215,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>god.motivacao</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>leandro._bjj</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -5218,24 +5246,24 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mmmarc20</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -5285,30 +5313,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>anaaj_camargo</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -5355,27 +5383,27 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tawanregismma</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tabajaraharu</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -5803,35 +5831,35 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>reifernandes</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5845,41 +5873,41 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -5887,21 +5915,21 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -5915,55 +5943,55 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -5971,35 +5999,35 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -6013,7 +6041,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -6027,21 +6055,21 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -6055,69 +6083,69 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -6125,13 +6153,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -6139,35 +6167,35 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -6181,7 +6209,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -6190,18 +6218,18 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -6209,13 +6237,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -6223,35 +6251,35 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>maca.mariotti</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>joegam3r</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -6265,7 +6293,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -6279,7 +6307,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -6293,21 +6321,21 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -6321,7 +6349,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6335,7 +6363,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6349,7 +6377,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6363,7 +6391,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6377,7 +6405,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6391,7 +6419,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6405,7 +6433,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>badboykillermma</v>
+        <v>graalino</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6419,7 +6447,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>lopesbrunao</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6433,7 +6461,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>cjrnavalha</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6447,21 +6475,21 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>treinaadorrafael</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6475,13 +6503,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6489,13 +6517,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6503,7 +6531,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6517,13 +6545,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -6531,13 +6559,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6545,13 +6573,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6559,7 +6587,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6573,7 +6601,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6587,7 +6615,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6601,7 +6629,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6615,7 +6643,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6629,7 +6657,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6643,7 +6671,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6657,7 +6685,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6671,7 +6699,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6685,7 +6713,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6699,7 +6727,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6713,13 +6741,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -6727,13 +6755,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ravenrodriguez___</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -8211,7 +8239,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8225,13 +8253,13 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -8239,7 +8267,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8253,7 +8281,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8267,21 +8295,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8295,7 +8323,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8309,21 +8337,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8337,21 +8365,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8365,7 +8393,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8379,21 +8407,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8407,7 +8435,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>giulia.fasolato</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8421,7 +8449,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ommariotti</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8435,7 +8463,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8449,7 +8477,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>brodschack_</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8458,12 +8486,12 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>helenaseveribjj</v>
+        <v>_vpft</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8472,12 +8500,12 @@
         <v>1</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>_kainanlima</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8491,7 +8519,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8505,7 +8533,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8519,7 +8547,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8533,7 +8561,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8547,7 +8575,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8561,7 +8589,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8575,7 +8603,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8589,7 +8617,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dadwillians</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8603,7 +8631,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8617,7 +8645,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>chubotaru_lilu</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8631,7 +8659,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8645,7 +8673,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8659,7 +8687,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8673,7 +8701,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8687,7 +8715,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8701,7 +8729,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8715,7 +8743,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8729,7 +8757,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8743,7 +8771,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8757,7 +8785,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8771,7 +8799,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8785,7 +8813,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8799,7 +8827,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8813,7 +8841,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8827,7 +8855,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8841,7 +8869,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8855,7 +8883,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8869,7 +8897,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8883,7 +8911,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8897,7 +8925,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8911,7 +8939,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8925,7 +8953,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8939,7 +8967,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8953,7 +8981,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -8967,7 +8995,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -8981,7 +9009,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -8995,7 +9023,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9009,7 +9037,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9023,7 +9051,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9037,7 +9065,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9051,7 +9079,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9065,7 +9093,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9079,7 +9107,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9093,7 +9121,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9107,7 +9135,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9121,7 +9149,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9135,7 +9163,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9149,7 +9177,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9163,7 +9191,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9177,7 +9205,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9191,7 +9219,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9205,7 +9233,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9219,7 +9247,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9233,7 +9261,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9247,7 +9275,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9261,7 +9289,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9275,7 +9303,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9289,7 +9317,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9303,7 +9331,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9317,7 +9345,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9331,7 +9359,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9345,7 +9373,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9359,7 +9387,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9373,7 +9401,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9387,7 +9415,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9401,7 +9429,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9415,7 +9443,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9429,7 +9457,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9443,7 +9471,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9457,7 +9485,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9471,7 +9499,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9485,7 +9513,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9499,21 +9527,49 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
         <v>meirelesmma</v>
       </c>
-      <c r="B325">
-        <v>0</v>
-      </c>
-      <c r="C325">
-        <v>1</v>
-      </c>
-      <c r="D325">
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D325"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D327"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>528</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -629,13 +629,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -657,13 +657,13 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -696,7 +696,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>alvesmidih</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B22">
         <v>15</v>
@@ -705,35 +705,35 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B23">
         <v>15</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>anaaj_camargo</v>
+        <v>tiwimma</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +825,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>karen.ottoni</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -1027,60 +1027,60 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1088,55 +1088,55 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>fabinho_falcao_</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1144,24 +1144,24 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B56">
         <v>4</v>
@@ -1186,21 +1186,21 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>shawlin13oficial</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -1242,49 +1242,49 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ravenrodriguez___</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>reifernandes</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1298,41 +1298,41 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -1340,21 +1340,21 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1368,55 +1368,55 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -1424,35 +1424,35 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1480,21 +1480,21 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -1508,55 +1508,55 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>douglasipvr_mma</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>tassiogiloficial</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -1564,21 +1564,21 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -1592,49 +1592,49 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fredoctmma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -1643,26 +1643,26 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>diegopaivajj</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>fabaotipster</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1676,35 +1676,35 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>maca.mariotti</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>badboykillermma</v>
+        <v>graalino</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>lopesbrunao</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>cjrnavalha</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -5008,13 +5008,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>528</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3">
@@ -5022,13 +5022,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4">
@@ -5078,13 +5078,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -5106,13 +5106,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -5218,13 +5218,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -5246,13 +5246,13 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -5285,7 +5285,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>alvesmidih</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B22">
         <v>15</v>
@@ -5294,35 +5294,35 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B23">
         <v>15</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>anaaj_camargo</v>
+        <v>tiwimma</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -5414,13 +5414,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -5607,7 +5607,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>karen.ottoni</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -5616,60 +5616,60 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -5677,55 +5677,55 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>fabinho_falcao_</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -5733,24 +5733,24 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B56">
         <v>4</v>
@@ -5775,21 +5775,21 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>shawlin13oficial</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -5817,13 +5817,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -5831,49 +5831,49 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ravenrodriguez___</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>reifernandes</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -5887,41 +5887,41 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -5929,21 +5929,21 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -5957,55 +5957,55 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -6013,35 +6013,35 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -6069,21 +6069,21 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -6097,55 +6097,55 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>douglasipvr_mma</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>tassiogiloficial</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -6153,21 +6153,21 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -6181,49 +6181,49 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fredoctmma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -6232,26 +6232,26 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>diegopaivajj</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>fabaotipster</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -6265,35 +6265,35 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>maca.mariotti</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -6335,21 +6335,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>badboykillermma</v>
+        <v>graalino</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>lopesbrunao</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>cjrnavalha</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B107">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -601,13 +601,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -699,13 +699,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -783,7 +783,7 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1130,27 +1130,27 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1158,24 +1158,24 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -1200,21 +1200,21 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>shawlin13oficial</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -1242,13 +1242,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1256,16 +1256,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ravenrodriguez___</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5008,13 +5008,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3">
@@ -5022,13 +5022,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -5078,13 +5078,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -5190,13 +5190,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -5288,13 +5288,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -5372,7 +5372,7 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -5719,27 +5719,27 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -5747,24 +5747,24 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -5789,21 +5789,21 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>shawlin13oficial</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -5831,13 +5831,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -5845,16 +5845,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ravenrodriguez___</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3">
@@ -674,10 +674,10 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -3608,21 +3608,21 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -3636,21 +3636,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,13 +3678,13 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,21 +3720,21 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,21 +3762,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,21 +3790,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,21 +3832,21 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>giulia.fasolato</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -5008,13 +5008,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3">
@@ -5263,10 +5263,10 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -8197,21 +8197,21 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -8225,21 +8225,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8267,13 +8267,13 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -8281,7 +8281,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8309,21 +8309,21 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8351,21 +8351,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8379,21 +8379,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8421,21 +8421,21 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>giulia.fasolato</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B248">
         <v>0</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>543</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -612,100 +612,100 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>aline.r15</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>aline.r15</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>god.motivacao</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>leandro._bjj</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
       <c r="C20">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>anaaj_camargo</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -797,38 +797,38 @@
         <v>tabajaraharu</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>9</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tawanregismma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>rm.nicki</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B31">
         <v>7</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -5008,13 +5008,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>543</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3">
@@ -5064,7 +5064,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5106,13 +5106,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -5201,100 +5201,100 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>aline.r15</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>aline.r15</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>god.motivacao</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>leandro._bjj</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
       <c r="C20">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B21">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>anaaj_camargo</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -5386,38 +5386,38 @@
         <v>tabajaraharu</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>9</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tawanregismma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>rm.nicki</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B31">
         <v>7</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>4</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>554</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -615,13 +615,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -643,41 +643,41 @@
         <v>combintel</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>god.motivacao</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>anaaj_camargo</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B20">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -752,72 +752,72 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>eliassilverio</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>7</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>cleyton_jesuss</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tabajaraharu</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>rm.nicki</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -920,83 +920,83 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gdazuera</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>enzoferrari680</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>eolucasrosa</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B42">
         <v>5</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1004,13 +1004,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1018,16 +1018,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>cjrnavalha</v>
+        <v>paxlucta</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -1223,12 +1223,12 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -1256,13 +1256,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -1270,35 +1270,35 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1312,41 +1312,41 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -1354,21 +1354,21 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,55 +1382,55 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -1438,35 +1438,35 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1494,21 +1494,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -1522,83 +1522,83 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>maca.mariotti</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ismaeldaniell</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -1606,13 +1606,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -1620,35 +1620,35 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1671,18 +1671,18 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -1690,13 +1690,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -1704,21 +1704,21 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1760,21 +1760,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>badboykillermma</v>
+        <v>graalino</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -5008,13 +5008,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>554</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3">
@@ -5064,7 +5064,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5078,13 +5078,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -5106,13 +5106,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -5190,13 +5190,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -5204,13 +5204,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -5232,41 +5232,41 @@
         <v>combintel</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>god.motivacao</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C19">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>anaaj_camargo</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B20">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -5341,72 +5341,72 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>eliassilverio</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>7</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>cleyton_jesuss</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>tabajaraharu</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>rm.nicki</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -5509,83 +5509,83 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gdazuera</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>enzoferrari680</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>eolucasrosa</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B42">
         <v>5</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -5593,13 +5593,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -5607,16 +5607,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>cjrnavalha</v>
+        <v>paxlucta</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -5803,7 +5803,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -5812,12 +5812,12 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -5845,13 +5845,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -5859,35 +5859,35 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -5901,41 +5901,41 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -5943,21 +5943,21 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -5971,55 +5971,55 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -6027,35 +6027,35 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -6069,7 +6069,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -6083,21 +6083,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -6111,83 +6111,83 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>maca.mariotti</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ismaeldaniell</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -6195,13 +6195,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -6209,35 +6209,35 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -6251,7 +6251,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -6260,18 +6260,18 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -6279,13 +6279,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -6293,21 +6293,21 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -6335,7 +6335,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -6349,21 +6349,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>badboykillermma</v>
+        <v>graalino</v>
       </c>
       <c r="B106">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D327"/>
+  <dimension ref="A1:D328"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>809</v>
+        <v>826</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>571</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>22</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -615,55 +615,55 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>aline.r15</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>aline.r15</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>anaaj_camargo</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -738,13 +738,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -752,16 +752,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>rm.nicki</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -864,30 +864,30 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>italothearcher</v>
+        <v>maxgandra</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>maxgandra</v>
+        <v>italothearcher</v>
       </c>
       <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35">
         <v>6</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1270,13 +1270,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -1284,35 +1284,35 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -1326,41 +1326,41 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -1368,21 +1368,21 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1396,55 +1396,55 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -1452,35 +1452,35 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -1508,21 +1508,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -1536,83 +1536,83 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>maca.mariotti</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ismaeldaniell</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -1634,35 +1634,35 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -1685,18 +1685,18 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -1704,13 +1704,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -1718,21 +1718,21 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1774,21 +1774,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,21 +1900,21 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -1942,13 +1942,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2180,35 +2180,35 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,13 +2250,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,35 +2572,35 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,13 +3314,13 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -3328,13 +3328,13 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,13 +3566,13 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -3594,21 +3594,21 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D229">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -3622,21 +3622,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -3650,21 +3650,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -3692,13 +3692,13 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,21 +3734,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,21 +3776,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,21 +3804,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,21 +3846,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3925,12 +3925,12 @@
         <v>1</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,28 +4966,42 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
         <v>dvlucc2k26_</v>
       </c>
-      <c r="B327">
-        <v>0</v>
-      </c>
-      <c r="C327">
-        <v>1</v>
-      </c>
-      <c r="D327">
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+      <c r="D328">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D327"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D328"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D327"/>
+  <dimension ref="A1:D328"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5008,13 +5022,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>809</v>
+        <v>826</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>571</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3">
@@ -5022,13 +5036,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4">
@@ -5050,13 +5064,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -5078,13 +5092,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -5106,13 +5120,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -5190,13 +5204,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>22</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -5204,55 +5218,55 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>aline.r15</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>aline.r15</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>anaaj_camargo</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -5327,13 +5341,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -5341,16 +5355,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>rm.nicki</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -5453,30 +5467,30 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>italothearcher</v>
+        <v>maxgandra</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>maxgandra</v>
+        <v>italothearcher</v>
       </c>
       <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35">
         <v>6</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -5859,13 +5873,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -5873,35 +5887,35 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -5915,41 +5929,41 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>edebetim_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -5957,21 +5971,21 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -5985,55 +5999,55 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>marcos_tailandess</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -6041,35 +6055,35 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -6083,7 +6097,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -6097,21 +6111,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -6125,83 +6139,83 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>maca.mariotti</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ismaeldaniell</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -6209,13 +6223,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -6223,35 +6237,35 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -6265,7 +6279,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -6274,18 +6288,18 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -6293,13 +6307,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -6307,21 +6321,21 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -6335,7 +6349,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -6349,7 +6363,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -6363,21 +6377,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6391,7 +6405,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6405,7 +6419,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6419,7 +6433,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6433,7 +6447,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6447,7 +6461,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6461,7 +6475,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6475,7 +6489,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6489,21 +6503,21 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6517,13 +6531,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6531,13 +6545,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -6545,7 +6559,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6559,13 +6573,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6573,13 +6587,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6587,13 +6601,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6601,7 +6615,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6615,7 +6629,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6629,7 +6643,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6643,7 +6657,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6657,7 +6671,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6671,7 +6685,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6685,7 +6699,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6699,7 +6713,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6713,7 +6727,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6727,7 +6741,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6741,7 +6755,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6755,13 +6769,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -6769,35 +6783,35 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6811,7 +6825,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6825,7 +6839,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6839,13 +6853,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -6853,7 +6867,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6867,7 +6881,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6881,7 +6895,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6895,7 +6909,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6909,7 +6923,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6923,7 +6937,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6937,7 +6951,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6951,7 +6965,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6965,7 +6979,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -6979,7 +6993,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -6993,7 +7007,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7007,7 +7021,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7021,7 +7035,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7035,7 +7049,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7049,7 +7063,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7063,7 +7077,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7077,7 +7091,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7091,7 +7105,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7105,7 +7119,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7119,7 +7133,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7133,7 +7147,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7147,7 +7161,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7161,35 +7175,35 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7203,7 +7217,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7217,7 +7231,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7231,7 +7245,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7245,7 +7259,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7259,7 +7273,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7273,7 +7287,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7287,7 +7301,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7301,7 +7315,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7315,7 +7329,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7329,7 +7343,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7343,7 +7357,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7357,7 +7371,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7371,7 +7385,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7385,7 +7399,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7399,7 +7413,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7413,7 +7427,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7427,7 +7441,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7441,7 +7455,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7455,7 +7469,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7469,7 +7483,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7483,7 +7497,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7497,7 +7511,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7511,7 +7525,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7525,7 +7539,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7539,7 +7553,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7553,7 +7567,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7567,7 +7581,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7581,7 +7595,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7595,7 +7609,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7609,7 +7623,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7623,7 +7637,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7637,7 +7651,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7651,7 +7665,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7665,7 +7679,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7679,7 +7693,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7693,7 +7707,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7707,7 +7721,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7721,7 +7735,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7735,7 +7749,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7749,7 +7763,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7763,7 +7777,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7777,7 +7791,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7791,7 +7805,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7805,7 +7819,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7819,7 +7833,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7847,7 +7861,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7861,7 +7875,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7875,7 +7889,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7889,7 +7903,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7903,13 +7917,13 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -7917,13 +7931,13 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -7931,7 +7945,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7973,7 +7987,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7987,7 +8001,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -8001,7 +8015,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -8015,7 +8029,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -8029,7 +8043,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -8043,7 +8057,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -8057,7 +8071,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8071,7 +8085,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8085,7 +8099,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8099,7 +8113,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8127,7 +8141,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8141,7 +8155,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -8155,13 +8169,13 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -8169,7 +8183,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -8183,21 +8197,21 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B229">
         <v>0</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D229">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -8211,21 +8225,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8239,21 +8253,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8267,7 +8281,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8281,13 +8295,13 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8309,7 +8323,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8323,21 +8337,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8351,7 +8365,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8365,21 +8379,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8393,21 +8407,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8421,7 +8435,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8435,21 +8449,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8463,7 +8477,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8477,7 +8491,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8491,7 +8505,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8505,7 +8519,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8514,12 +8528,12 @@
         <v>1</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8533,7 +8547,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8547,7 +8561,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8561,7 +8575,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8575,7 +8589,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8589,7 +8603,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8603,7 +8617,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8617,7 +8631,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9555,21 +9569,35 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
         <v>dvlucc2k26_</v>
       </c>
-      <c r="B327">
-        <v>0</v>
-      </c>
-      <c r="C327">
-        <v>1</v>
-      </c>
-      <c r="D327">
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+      <c r="D328">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D327"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D328"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -615,55 +615,55 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>anaaj_camargo</v>
+        <v>combintel</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>aline.r15</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>aline.r15</v>
       </c>
       <c r="B19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -5022,13 +5022,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3">
@@ -5036,13 +5036,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -5120,13 +5120,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -5218,55 +5218,55 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>anaaj_camargo</v>
+        <v>combintel</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>aline.r15</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>aline.r15</v>
       </c>
       <c r="B19">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>24</v>
@@ -626,30 +626,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>combintel</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>anaaj_camargo</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -710,7 +710,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>alvesmidih</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -719,35 +719,35 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B24">
         <v>15</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>rm.nicki</v>
+        <v>tiwimma</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -836,100 +836,100 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>italothearcher</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
         <v>4</v>
-      </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>vndcardoso</v>
+        <v>italothearcher</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>cjrnavalha</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -5022,13 +5022,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3">
@@ -5092,13 +5092,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -5207,7 +5207,7 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>24</v>
@@ -5229,30 +5229,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>combintel</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>anaaj_camargo</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -5313,7 +5313,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>alvesmidih</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -5322,35 +5322,35 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B24">
         <v>15</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>rm.nicki</v>
+        <v>tiwimma</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -5439,100 +5439,100 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>italothearcher</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
         <v>4</v>
-      </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>vndcardoso</v>
+        <v>italothearcher</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>cjrnavalha</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>604</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -612,30 +612,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -682,44 +682,44 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>leandro._bjj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>rm.nicki</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -780,13 +780,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>pedromadeira.s</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -794,16 +794,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>cleyton_jesuss</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -836,58 +836,58 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>maxgandra</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>cjrnavalha</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -1461,40 +1461,40 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1522,21 +1522,21 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -1550,30 +1550,30 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>maca.mariotti</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5022,13 +5022,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>604</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3">
@@ -5036,13 +5036,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -5078,13 +5078,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -5106,13 +5106,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -5215,30 +5215,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -5285,44 +5285,44 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>leandro._bjj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>rm.nicki</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -5383,13 +5383,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>pedromadeira.s</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -5397,16 +5397,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>cleyton_jesuss</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -5439,58 +5439,58 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>maxgandra</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>cjrnavalha</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -6055,7 +6055,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -6064,40 +6064,40 @@
         <v>5</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -6125,21 +6125,21 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -6153,30 +6153,30 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>maca.mariotti</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D328"/>
+  <dimension ref="A1:D329"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -542,30 +542,30 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B11">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ronemayanmorais</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -668,30 +668,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>god.motivacao</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>rm.nicki</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>98</v>
+      </c>
+      <c r="D21">
         <v>18</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -766,13 +766,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B27">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -780,16 +780,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>cleyton_jesuss</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -797,7 +797,7 @@
         <v>pedromadeira.s</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1032,30 +1032,30 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3580,13 +3580,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>marinealcausa</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -3608,21 +3608,21 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D230">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -3636,21 +3636,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -3664,21 +3664,21 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,13 +3706,13 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,21 +3748,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,21 +3790,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,21 +3818,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,21 +3860,21 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3939,12 +3939,12 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,28 +4980,42 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
         <v>dvlucc2k26_</v>
       </c>
-      <c r="B328">
-        <v>0</v>
-      </c>
-      <c r="C328">
-        <v>1</v>
-      </c>
-      <c r="D328">
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+      <c r="D329">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D328"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D329"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D328"/>
+  <dimension ref="A1:D329"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5022,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>622</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3">
@@ -5036,13 +5050,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -5092,7 +5106,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -5120,13 +5134,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -5145,30 +5159,30 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B11">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ronemayanmorais</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5218,7 +5232,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5271,30 +5285,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>god.motivacao</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>rm.nicki</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>98</v>
+      </c>
+      <c r="D21">
         <v>18</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -5369,13 +5383,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B27">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -5383,16 +5397,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>cleyton_jesuss</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -5400,7 +5414,7 @@
         <v>pedromadeira.s</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -5442,7 +5456,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -5635,30 +5649,30 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -8183,13 +8197,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>marinealcausa</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -8197,7 +8211,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -8211,21 +8225,21 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D230">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -8239,21 +8253,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8267,21 +8281,21 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8309,13 +8323,13 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -8323,7 +8337,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8337,7 +8351,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8351,21 +8365,21 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8379,7 +8393,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8393,21 +8407,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8421,21 +8435,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8463,21 +8477,21 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8491,7 +8505,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8505,7 +8519,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8519,7 +8533,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8533,7 +8547,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8542,12 +8556,12 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8561,7 +8575,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8575,7 +8589,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8589,7 +8603,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8603,7 +8617,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8617,7 +8631,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9555,7 +9569,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9569,7 +9583,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -9583,21 +9597,35 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
         <v>dvlucc2k26_</v>
       </c>
-      <c r="B328">
-        <v>0</v>
-      </c>
-      <c r="C328">
-        <v>1</v>
-      </c>
-      <c r="D328">
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+      <c r="D329">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D328"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D329"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -640,44 +640,44 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>aline.r15</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>rm.nicki</v>
+        <v>aline.r15</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -5036,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3">
@@ -5050,13 +5050,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -5257,44 +5257,44 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>aline.r15</v>
+        <v>combintel</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>rm.nicki</v>
+        <v>aline.r15</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,7 +419,7 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -615,7 +615,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -688,10 +688,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -822,27 +822,27 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>tawanregismma</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>cjrnavalha</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B32">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -1340,41 +1340,41 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>edebetim_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -1382,21 +1382,21 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -1410,63 +1410,63 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -1475,40 +1475,40 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,21 +1536,21 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -1564,69 +1564,69 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -1648,35 +1648,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -1699,18 +1699,18 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -1718,13 +1718,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -1732,21 +1732,21 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1788,21 +1788,21 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,21 +1914,21 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,13 +1942,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,13 +2180,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2194,35 +2194,35 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D129">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,13 +2264,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,35 +2586,35 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,13 +3328,13 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -3342,13 +3342,13 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>_beegomes_</v>
+        <v>turmanmma</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -5036,7 +5036,7 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -5092,13 +5092,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -5232,7 +5232,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5246,7 +5246,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5305,10 +5305,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -5439,27 +5439,27 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>tawanregismma</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>cjrnavalha</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B32">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -5957,41 +5957,41 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>edebetim_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -5999,21 +5999,21 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -6027,63 +6027,63 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -6092,40 +6092,40 @@
         <v>5</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -6153,21 +6153,21 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -6181,69 +6181,69 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -6251,13 +6251,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -6265,35 +6265,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -6316,18 +6316,18 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -6335,13 +6335,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -6349,21 +6349,21 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -6405,21 +6405,21 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6531,21 +6531,21 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6559,13 +6559,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -6573,13 +6573,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -6587,7 +6587,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6601,13 +6601,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6615,13 +6615,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>benjafloripabjj</v>
+        <v>030sami</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6629,13 +6629,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6797,13 +6797,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -6811,35 +6811,35 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D129">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6881,13 +6881,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>alerrandrojj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7049,7 +7049,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7203,35 +7203,35 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7749,7 +7749,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7861,7 +7861,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7875,7 +7875,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7917,7 +7917,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7945,13 +7945,13 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -7959,13 +7959,13 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -8015,7 +8015,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -8029,7 +8029,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -8043,7 +8043,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -8071,7 +8071,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -8085,7 +8085,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8099,7 +8099,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8127,7 +8127,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8141,7 +8141,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8155,7 +8155,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -8197,7 +8197,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>_beegomes_</v>
+        <v>turmanmma</v>
       </c>
       <c r="B228">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -688,10 +688,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D21">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -2012,27 +2012,27 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,13 +2194,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -2208,35 +2208,35 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -5305,10 +5305,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D21">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -6629,27 +6629,27 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6811,13 +6811,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -6825,35 +6825,35 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6895,13 +6895,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B143">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -517,7 +517,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -584,30 +584,30 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>kaua_limamma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ryangandraufc</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5036,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3">
@@ -5050,13 +5050,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -5106,7 +5106,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -5134,7 +5134,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5201,30 +5201,30 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>kaua_limamma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ryangandraufc</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C15">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5246,7 +5246,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3">
@@ -5036,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
@@ -643,13 +643,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -5036,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3">
@@ -5050,13 +5050,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
@@ -5260,13 +5260,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -590,10 +590,10 @@
         <v>33</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -612,30 +612,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -657,13 +657,13 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -752,30 +752,30 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>cleyton_jesuss</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -814,10 +814,10 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -825,7 +825,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>652</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3">
@@ -5050,13 +5050,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
@@ -5106,13 +5106,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -5134,13 +5134,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -5207,10 +5207,10 @@
         <v>33</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -5229,30 +5229,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -5274,13 +5274,13 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -5369,30 +5369,30 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>cleyton_jesuss</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -5431,10 +5431,10 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -5442,7 +5442,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>0</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
@@ -5036,13 +5036,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3">
@@ -5050,13 +5050,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D329"/>
+  <dimension ref="A1:D331"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +590,7 @@
         <v>33</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>25</v>
@@ -612,30 +612,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -643,13 +643,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -1032,13 +1032,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1046,24 +1046,24 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1074,27 +1074,27 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -1102,41 +1102,41 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -1144,27 +1144,27 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1172,24 +1172,24 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B58">
         <v>4</v>
@@ -1214,21 +1214,21 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -1237,12 +1237,12 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1284,13 +1284,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -1298,35 +1298,35 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -1340,55 +1340,55 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>_beegomes_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>edebetim_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -1396,21 +1396,21 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1424,63 +1424,63 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -1489,40 +1489,40 @@
         <v>5</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1550,21 +1550,21 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -1578,69 +1578,69 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -1648,13 +1648,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -1662,35 +1662,35 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1713,18 +1713,18 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -1732,13 +1732,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1802,21 +1802,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,21 +1928,21 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2012,41 +2012,41 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,13 +2208,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -2222,35 +2222,35 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,13 +2292,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,35 +2600,35 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,13 +3342,13 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -3356,13 +3356,13 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,13 +3594,13 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -3622,21 +3622,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D231">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -3650,21 +3650,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,21 +3678,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,13 +3720,13 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,21 +3762,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,21 +3804,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,21 +3832,21 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,21 +3874,21 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3953,12 +3953,12 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,28 +4994,56 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
         <v>dvlucc2k26_</v>
       </c>
-      <c r="B329">
-        <v>0</v>
-      </c>
-      <c r="C329">
-        <v>1</v>
-      </c>
-      <c r="D329">
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>armysenju</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+      <c r="D331">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D329"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D331"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D329"/>
+  <dimension ref="A1:D331"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5036,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5162,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -5207,7 +5235,7 @@
         <v>33</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14">
         <v>25</v>
@@ -5229,30 +5257,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B16">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -5260,13 +5288,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -5649,13 +5677,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -5663,24 +5691,24 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5691,27 +5719,27 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -5719,41 +5747,41 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -5761,27 +5789,27 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -5789,24 +5817,24 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5817,7 +5845,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B58">
         <v>4</v>
@@ -5831,21 +5859,21 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -5854,12 +5882,12 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -5873,7 +5901,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -5887,7 +5915,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5901,13 +5929,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -5915,35 +5943,35 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -5957,55 +5985,55 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>_beegomes_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>edebetim_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>alexsandra_kairos</v>
+        <v>edebetim_</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6013,21 +6041,21 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -6041,63 +6069,63 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -6106,40 +6134,40 @@
         <v>5</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>adriano.trator</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -6153,7 +6181,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -6167,21 +6195,21 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -6195,69 +6223,69 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -6265,13 +6293,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -6279,35 +6307,35 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -6321,7 +6349,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -6330,18 +6358,18 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -6349,13 +6377,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -6363,21 +6391,21 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -6391,7 +6419,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -6405,7 +6433,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -6419,21 +6447,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6447,7 +6475,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6461,7 +6489,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6475,7 +6503,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6489,7 +6517,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6503,7 +6531,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6517,7 +6545,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6531,7 +6559,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6545,21 +6573,21 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6573,13 +6601,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -6587,13 +6615,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6601,7 +6629,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6615,13 +6643,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6629,41 +6657,41 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -6671,7 +6699,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6685,7 +6713,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6699,7 +6727,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6713,7 +6741,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6727,7 +6755,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6741,7 +6769,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6755,7 +6783,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6769,7 +6797,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6783,7 +6811,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6797,7 +6825,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6811,7 +6839,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6825,13 +6853,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -6839,35 +6867,35 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D131">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6881,7 +6909,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6895,7 +6923,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6909,13 +6937,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -6923,7 +6951,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6937,7 +6965,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6951,7 +6979,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6965,7 +6993,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -6979,7 +7007,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6993,7 +7021,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7007,7 +7035,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7021,7 +7049,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7035,7 +7063,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7049,7 +7077,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7063,7 +7091,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7077,7 +7105,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7091,7 +7119,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7105,7 +7133,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7119,7 +7147,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7133,7 +7161,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7147,7 +7175,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7161,7 +7189,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7175,7 +7203,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7189,7 +7217,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7203,7 +7231,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7217,35 +7245,35 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7259,7 +7287,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7273,7 +7301,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7287,7 +7315,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7301,7 +7329,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7315,7 +7343,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7329,7 +7357,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7343,7 +7371,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7357,7 +7385,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7371,7 +7399,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7385,7 +7413,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7399,7 +7427,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7413,7 +7441,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7427,7 +7455,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7441,7 +7469,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7455,7 +7483,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7469,7 +7497,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7483,7 +7511,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7497,7 +7525,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7511,7 +7539,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7525,7 +7553,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7539,7 +7567,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7553,7 +7581,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7567,7 +7595,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7581,7 +7609,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7595,7 +7623,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7609,7 +7637,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7623,7 +7651,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7637,7 +7665,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7651,7 +7679,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7665,7 +7693,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7679,7 +7707,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7693,7 +7721,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7707,7 +7735,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7721,7 +7749,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7735,7 +7763,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7749,7 +7777,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7763,7 +7791,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7777,7 +7805,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7791,7 +7819,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7805,7 +7833,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7819,7 +7847,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7833,7 +7861,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7847,7 +7875,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7861,7 +7889,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7875,7 +7903,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7889,7 +7917,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7903,7 +7931,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7917,7 +7945,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7931,7 +7959,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7945,7 +7973,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7959,13 +7987,13 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -7973,13 +8001,13 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -7987,7 +8015,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -8001,7 +8029,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -8015,7 +8043,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -8029,7 +8057,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -8043,7 +8071,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -8057,7 +8085,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -8071,7 +8099,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -8085,7 +8113,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8099,7 +8127,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8113,7 +8141,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8127,7 +8155,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8141,7 +8169,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8155,7 +8183,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8169,7 +8197,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -8183,7 +8211,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -8197,7 +8225,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -8211,13 +8239,13 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -8225,7 +8253,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -8239,21 +8267,21 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B231">
         <v>0</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D231">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8267,21 +8295,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8295,21 +8323,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8323,7 +8351,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8337,13 +8365,13 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -8351,7 +8379,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8365,7 +8393,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8379,21 +8407,21 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8407,7 +8435,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8421,21 +8449,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8449,21 +8477,21 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8477,7 +8505,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8491,21 +8519,21 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8519,7 +8547,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8533,7 +8561,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8547,7 +8575,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8561,7 +8589,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8570,12 +8598,12 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8589,7 +8617,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8603,7 +8631,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8617,7 +8645,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8631,7 +8659,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8645,7 +8673,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8659,7 +8687,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8673,7 +8701,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8687,7 +8715,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8701,7 +8729,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8715,7 +8743,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8729,7 +8757,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8743,7 +8771,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8757,7 +8785,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8771,7 +8799,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8785,7 +8813,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8799,7 +8827,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8813,7 +8841,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8827,7 +8855,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8841,7 +8869,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8855,7 +8883,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8869,7 +8897,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8883,7 +8911,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8897,7 +8925,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8911,7 +8939,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8925,7 +8953,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8939,7 +8967,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8953,7 +8981,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8967,7 +8995,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -8981,7 +9009,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -8995,7 +9023,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -9009,7 +9037,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9023,7 +9051,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9037,7 +9065,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9051,7 +9079,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9065,7 +9093,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9079,7 +9107,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9093,7 +9121,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9107,7 +9135,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9121,7 +9149,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9135,7 +9163,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9149,7 +9177,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9163,7 +9191,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9177,7 +9205,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9191,7 +9219,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9205,7 +9233,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9219,7 +9247,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9233,7 +9261,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9247,7 +9275,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9261,7 +9289,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9275,7 +9303,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9289,7 +9317,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9303,7 +9331,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9317,7 +9345,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9331,7 +9359,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9345,7 +9373,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9359,7 +9387,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9373,7 +9401,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9387,7 +9415,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9401,7 +9429,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9415,7 +9443,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9429,7 +9457,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9443,7 +9471,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9457,7 +9485,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9471,7 +9499,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9485,7 +9513,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9499,7 +9527,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9513,7 +9541,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9527,7 +9555,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9541,7 +9569,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9555,7 +9583,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9569,7 +9597,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9583,7 +9611,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -9597,7 +9625,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -9611,21 +9639,49 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
         <v>dvlucc2k26_</v>
       </c>
-      <c r="B329">
-        <v>0</v>
-      </c>
-      <c r="C329">
-        <v>1</v>
-      </c>
-      <c r="D329">
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>armysenju</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+      <c r="D331">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D329"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D331"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>669</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -570,58 +570,58 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>erik_.mma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B14">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>kaua_limamma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B15">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>anaaj_camargo</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B16">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -643,13 +643,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +657,7 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -724,44 +724,44 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>alvesmidih</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B25">
         <v>15</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>cleyton_jesuss</v>
+        <v>tiwimma</v>
       </c>
       <c r="B26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1116,41 +1116,41 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1158,27 +1158,27 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1186,24 +1186,24 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B59">
         <v>4</v>
@@ -1228,21 +1228,21 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -1251,12 +1251,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1298,13 +1298,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1312,35 +1312,35 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1354,30 +1354,30 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>_beegomes_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>edebetim_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -5064,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>669</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3">
@@ -5078,13 +5078,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -5134,7 +5134,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -5148,13 +5148,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -5215,58 +5215,58 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>erik_.mma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B14">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>kaua_limamma</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B15">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>anaaj_camargo</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B16">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5288,13 +5288,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B18">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -5302,7 +5302,7 @@
         <v>combintel</v>
       </c>
       <c r="B19">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5369,44 +5369,44 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>alvesmidih</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B25">
         <v>15</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>cleyton_jesuss</v>
+        <v>tiwimma</v>
       </c>
       <c r="B26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -5761,41 +5761,41 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -5803,27 +5803,27 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -5831,24 +5831,24 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B59">
         <v>4</v>
@@ -5873,21 +5873,21 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -5896,12 +5896,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -5915,7 +5915,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -5943,13 +5943,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -5957,35 +5957,35 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -5999,30 +5999,30 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>_beegomes_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>edebetim_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>683</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -542,72 +542,72 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ronemayanmorais</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B11">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>bellsouza816</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B13">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>anaaj_camargo</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B15">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -626,30 +626,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>rm.nicki</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -727,7 +727,7 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -1102,13 +1102,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>_oliveira09_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -1116,55 +1116,55 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
         <v>3</v>
-      </c>
-      <c r="D52">
-        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1172,27 +1172,27 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1200,24 +1200,24 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B60">
         <v>4</v>
@@ -1242,21 +1242,21 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1265,12 +1265,12 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1312,13 +1312,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -1326,35 +1326,35 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1368,16 +1368,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>_beegomes_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -5064,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>683</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3">
@@ -5078,13 +5078,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
@@ -5187,72 +5187,72 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ronemayanmorais</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B11">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>bellsouza816</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B12">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B13">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>anaaj_camargo</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B15">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5271,30 +5271,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>rm.nicki</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B18">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -5372,7 +5372,7 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -5747,13 +5747,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>_oliveira09_</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -5761,55 +5761,55 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
         <v>3</v>
-      </c>
-      <c r="D52">
-        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -5817,27 +5817,27 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -5845,24 +5845,24 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B60">
         <v>4</v>
@@ -5887,21 +5887,21 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -5910,12 +5910,12 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -5957,13 +5957,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -5971,35 +5971,35 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -6013,16 +6013,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>_beegomes_</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3">
@@ -5064,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>694</v>
+        <v>709</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -542,30 +542,30 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ryangandraufc</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>anaaj_camargo</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -598,24 +598,24 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>erik_.mma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B15">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>kaua_limamma</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B16">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -626,16 +626,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>rm.nicki</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B17">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -696,44 +696,44 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>leandro._bjj</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>cleyton_jesuss</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1004,27 +1004,27 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>dagestan0920</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1032,27 +1032,27 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -1060,24 +1060,24 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1088,21 +1088,21 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>_beegomes_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -5064,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>694</v>
+        <v>709</v>
       </c>
     </row>
     <row r="3">
@@ -5078,7 +5078,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -5092,13 +5092,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C4">
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -5162,13 +5162,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -5187,30 +5187,30 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ryangandraufc</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>anaaj_camargo</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -5243,24 +5243,24 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>erik_.mma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B15">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>kaua_limamma</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B16">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5271,16 +5271,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>rm.nicki</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B17">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5341,44 +5341,44 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>leandro._bjj</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>cleyton_jesuss</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -5649,27 +5649,27 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>dagestan0920</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -5677,27 +5677,27 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -5705,24 +5705,24 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -5733,21 +5733,21 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>_beegomes_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B51">
         <v>3</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>948</v>
+        <v>965</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>709</v>
+        <v>726</v>
       </c>
     </row>
     <row r="3">
@@ -436,10 +436,10 @@
         <v>306</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4">
@@ -450,10 +450,10 @@
         <v>313</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -517,41 +517,41 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>irmandadefightteam</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>anaaj_camargo</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B11">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -570,44 +570,44 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ronemayanmorais</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B13">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>rm.nicki</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B15">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -688,10 +688,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -808,30 +808,30 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tabajaraharu</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
         <v>6</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>cjrnavalha</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -906,114 +906,114 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>vndcardoso</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B37">
         <v>5</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>gdazuera</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>enzoferrari680</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>eolucasrosa</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>_beegomes_</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1228,21 +1228,21 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lipe.ftt</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B61">
         <v>4</v>
@@ -1256,21 +1256,21 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -1279,12 +1279,12 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -1326,13 +1326,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -1340,35 +1340,35 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,27 +1382,27 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1410,21 +1410,21 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -1438,63 +1438,63 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -5064,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>948</v>
+        <v>965</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>709</v>
+        <v>726</v>
       </c>
     </row>
     <row r="3">
@@ -5081,10 +5081,10 @@
         <v>306</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4">
@@ -5095,10 +5095,10 @@
         <v>313</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -5134,7 +5134,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -5162,41 +5162,41 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>irmandadefightteam</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>anaaj_camargo</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B11">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5215,44 +5215,44 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ronemayanmorais</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B13">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>rm.nicki</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B15">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -5453,30 +5453,30 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tabajaraharu</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
         <v>6</v>
-      </c>
-      <c r="C30">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>cjrnavalha</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -5551,114 +5551,114 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>vndcardoso</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B37">
         <v>5</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>gdazuera</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>enzoferrari680</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>eolucasrosa</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>_beegomes_</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -5873,21 +5873,21 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>lipe.ftt</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B61">
         <v>4</v>
@@ -5901,21 +5901,21 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5924,12 +5924,12 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -5957,7 +5957,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -5971,13 +5971,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -5985,35 +5985,35 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -6027,27 +6027,27 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6055,21 +6055,21 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -6083,63 +6083,63 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>marcos_tailandess</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -6148,7 +6148,7 @@
         <v>5</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="3">
@@ -531,13 +531,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -556,30 +556,30 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ryangandraufc</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B12">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>36</v>
-      </c>
-      <c r="C12">
-        <v>27</v>
-      </c>
-      <c r="D12">
-        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>rm.nicki</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -5064,13 +5064,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="3">
@@ -5176,13 +5176,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -5201,30 +5201,30 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ryangandraufc</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B12">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>36</v>
-      </c>
-      <c r="C12">
-        <v>27</v>
-      </c>
-      <c r="D12">
-        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>rm.nicki</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D331"/>
+  <dimension ref="A1:D332"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>972</v>
+        <v>989</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>733</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -531,41 +531,41 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>irmandadefightteam</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>rm.nicki</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B12">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -962,44 +962,44 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>enzoferrari680</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1060,13 +1060,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1074,24 +1074,24 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1102,27 +1102,27 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -1130,55 +1130,55 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
+        <v>4</v>
+      </c>
+      <c r="D53">
         <v>3</v>
-      </c>
-      <c r="D53">
-        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1186,27 +1186,27 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1214,49 +1214,49 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>marcos_tailandess</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lipe.ftt</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -1270,21 +1270,21 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -1293,12 +1293,12 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -1340,13 +1340,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -1354,35 +1354,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1396,27 +1396,27 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1424,21 +1424,21 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -1452,91 +1452,91 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>adriano.trator</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -1564,21 +1564,21 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -1592,69 +1592,69 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -1662,13 +1662,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -1676,35 +1676,35 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -1727,18 +1727,18 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -1746,13 +1746,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -1760,21 +1760,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1816,21 +1816,21 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,21 +1942,21 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -2026,41 +2026,41 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,13 +2222,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -2236,35 +2236,35 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,13 +2306,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,35 +2614,35 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,13 +3356,13 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -3370,13 +3370,13 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,13 +3608,13 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -3636,21 +3636,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D232">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -3664,21 +3664,21 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -3692,21 +3692,21 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,13 +3734,13 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,21 +3776,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,21 +3818,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,21 +3846,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,21 +3888,21 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
       <c r="C250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3967,12 +3967,12 @@
         <v>1</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,28 +5022,42 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B331">
-        <v>0</v>
-      </c>
-      <c r="C331">
-        <v>1</v>
-      </c>
-      <c r="D331">
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D332"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D331"/>
+  <dimension ref="A1:D332"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5064,13 +5078,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>972</v>
+        <v>989</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>733</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3">
@@ -5078,13 +5092,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
@@ -5106,13 +5120,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -5120,13 +5134,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -5134,13 +5148,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -5148,13 +5162,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -5176,41 +5190,41 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>irmandadefightteam</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>rm.nicki</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B12">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5607,44 +5621,44 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>enzoferrari680</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5705,13 +5719,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -5719,24 +5733,24 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5747,27 +5761,27 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -5775,55 +5789,55 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
+        <v>4</v>
+      </c>
+      <c r="D53">
         <v>3</v>
-      </c>
-      <c r="D53">
-        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -5831,27 +5845,27 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -5859,49 +5873,49 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>marcos_tailandess</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>lipe.ftt</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B62">
         <v>4</v>
@@ -5915,21 +5929,21 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>shawlin13oficial</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -5938,12 +5952,12 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -5957,7 +5971,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -5971,7 +5985,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -5985,13 +5999,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -5999,35 +6013,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -6041,27 +6055,27 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6069,21 +6083,21 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -6097,91 +6111,91 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>adriano.trator</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -6195,7 +6209,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -6209,21 +6223,21 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -6237,69 +6251,69 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -6307,13 +6321,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -6321,35 +6335,35 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -6363,7 +6377,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -6372,18 +6386,18 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -6391,13 +6405,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -6405,21 +6419,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -6433,7 +6447,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -6447,7 +6461,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -6461,21 +6475,21 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6489,7 +6503,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6503,7 +6517,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6517,7 +6531,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6531,7 +6545,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6545,7 +6559,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6559,7 +6573,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6573,7 +6587,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6587,21 +6601,21 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>treinaadorrafael</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6615,13 +6629,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6629,13 +6643,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6643,7 +6657,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6657,13 +6671,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -6671,41 +6685,41 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -6713,7 +6727,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6727,7 +6741,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6741,7 +6755,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6755,7 +6769,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6769,7 +6783,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6783,7 +6797,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6797,7 +6811,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6811,7 +6825,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6825,7 +6839,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6839,7 +6853,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6853,7 +6867,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6867,13 +6881,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -6881,35 +6895,35 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D132">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6923,7 +6937,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6937,7 +6951,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6951,13 +6965,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -6965,7 +6979,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -6979,7 +6993,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -6993,7 +7007,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7007,7 +7021,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7021,7 +7035,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7035,7 +7049,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7049,7 +7063,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7063,7 +7077,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7077,7 +7091,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7091,7 +7105,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7105,7 +7119,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7119,7 +7133,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7133,7 +7147,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7147,7 +7161,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7161,7 +7175,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7175,7 +7189,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7189,7 +7203,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7203,7 +7217,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7217,7 +7231,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7231,7 +7245,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7245,7 +7259,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7259,35 +7273,35 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7301,7 +7315,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7315,7 +7329,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7329,7 +7343,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7343,7 +7357,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7357,7 +7371,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7371,7 +7385,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7385,7 +7399,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7399,7 +7413,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7413,7 +7427,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7427,7 +7441,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7441,7 +7455,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7455,7 +7469,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7469,7 +7483,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7483,7 +7497,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7497,7 +7511,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7511,7 +7525,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7525,7 +7539,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7539,7 +7553,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7553,7 +7567,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7567,7 +7581,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7581,7 +7595,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7595,7 +7609,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7609,7 +7623,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7623,7 +7637,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7637,7 +7651,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7651,7 +7665,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7665,7 +7679,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7679,7 +7693,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7693,7 +7707,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7707,7 +7721,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7721,7 +7735,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7735,7 +7749,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7749,7 +7763,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7763,7 +7777,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7777,7 +7791,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7791,7 +7805,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7805,7 +7819,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7819,7 +7833,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7847,7 +7861,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7861,7 +7875,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7875,7 +7889,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7889,7 +7903,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7903,7 +7917,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7917,7 +7931,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7931,7 +7945,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7973,7 +7987,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7987,7 +8001,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -8001,13 +8015,13 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -8015,13 +8029,13 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -8029,7 +8043,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -8043,7 +8057,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -8057,7 +8071,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -8071,7 +8085,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -8085,7 +8099,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -8099,7 +8113,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8127,7 +8141,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8141,7 +8155,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8155,7 +8169,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8169,7 +8183,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8183,7 +8197,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8197,7 +8211,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -8211,7 +8225,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -8225,7 +8239,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -8239,7 +8253,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -8253,13 +8267,13 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>marinealcausa</v>
+        <v>turmanmma</v>
       </c>
       <c r="B230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -8267,7 +8281,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -8281,21 +8295,21 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D232">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8309,21 +8323,21 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8337,21 +8351,21 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8365,7 +8379,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8379,13 +8393,13 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -8393,7 +8407,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8407,7 +8421,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8421,21 +8435,21 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8463,21 +8477,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8491,21 +8505,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8519,7 +8533,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8533,21 +8547,21 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
       <c r="C250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8561,7 +8575,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8575,7 +8589,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8589,7 +8603,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8603,7 +8617,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8612,12 +8626,12 @@
         <v>1</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9555,7 +9569,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9569,7 +9583,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9583,7 +9597,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9597,7 +9611,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9611,7 +9625,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -9625,7 +9639,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -9639,7 +9653,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -9653,7 +9667,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -9667,21 +9681,35 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B331">
-        <v>0</v>
-      </c>
-      <c r="C331">
-        <v>1</v>
-      </c>
-      <c r="D331">
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D331"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D332"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -587,13 +587,13 @@
         <v>ronemayanmorais</v>
       </c>
       <c r="B14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -643,13 +643,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -828,10 +828,10 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -5078,13 +5078,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="3">
@@ -5092,13 +5092,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -5176,13 +5176,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -5190,13 +5190,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -5246,13 +5246,13 @@
         <v>ronemayanmorais</v>
       </c>
       <c r="B14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -5302,13 +5302,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -5487,10 +5487,10 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">
@@ -5092,13 +5092,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>751</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3">
@@ -475,13 +475,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -850,181 +850,181 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>maxgandra</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>_beegomes_</v>
+        <v>italothearcher</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>vndcardoso</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>gdazuera</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>enzoferrari680</v>
+        <v>gdazuera</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B45">
         <v>5</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -1032,13 +1032,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1046,21 +1046,21 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>hugo7jj</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -1074,13 +1074,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1088,24 +1088,24 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1116,27 +1116,27 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -1144,55 +1144,55 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54">
         <v>3</v>
-      </c>
-      <c r="D54">
-        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -1200,27 +1200,27 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1228,49 +1228,49 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>marcos_tailandess</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lipe.ftt</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -1284,16 +1284,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5078,13 +5078,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>751</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5134,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -5509,181 +5509,181 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>maxgandra</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>_beegomes_</v>
+        <v>italothearcher</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>vndcardoso</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>gdazuera</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>enzoferrari680</v>
+        <v>gdazuera</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B45">
         <v>5</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -5691,13 +5691,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -5705,21 +5705,21 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>hugo7jj</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -5733,13 +5733,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -5747,24 +5747,24 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>karen.ottoni</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>glm.barbosa</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5775,27 +5775,27 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -5803,55 +5803,55 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54">
         <v>3</v>
-      </c>
-      <c r="D54">
-        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -5859,27 +5859,27 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -5887,49 +5887,49 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>marcos_tailandess</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>lipe.ftt</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -5943,16 +5943,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>badboykillermma</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D333"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>760</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
+        <v>46</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
         <v>44</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -573,13 +573,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -699,41 +699,41 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>leandro._bjj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -836,100 +836,100 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>tawanregismma</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B32">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>hugo7jj</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>_beegomes_</v>
+        <v>italothearcher</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -3622,13 +3622,13 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C231">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -3650,21 +3650,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D233">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,21 +3678,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,21 +3706,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,21 +3790,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,21 +3832,21 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,21 +3860,21 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,21 +3902,21 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B251">
         <v>0</v>
       </c>
       <c r="C251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3981,12 +3981,12 @@
         <v>1</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,28 +5036,42 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B332">
-        <v>0</v>
-      </c>
-      <c r="C332">
-        <v>1</v>
-      </c>
-      <c r="D332">
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+      <c r="D333">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D332"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D333"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D332"/>
+  <dimension ref="A1:D333"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5078,13 +5092,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>760</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3">
@@ -5092,13 +5106,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
@@ -5204,13 +5218,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
+        <v>46</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
         <v>44</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -5232,13 +5246,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -5358,41 +5372,41 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>leandro._bjj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>gra_jpereira</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -5495,100 +5509,100 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>tawanregismma</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B32">
         <v>7</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>hugo7jj</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>rrafaelins</v>
+        <v>maxgandra</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>_beegomes_</v>
+        <v>italothearcher</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -8281,13 +8295,13 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C231">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8309,21 +8323,21 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D233">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8337,21 +8351,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8365,21 +8379,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8393,7 +8407,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8407,13 +8421,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240">
         <v>1</v>
@@ -8421,7 +8435,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8435,7 +8449,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8449,21 +8463,21 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8477,7 +8491,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8491,21 +8505,21 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8519,21 +8533,21 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8547,7 +8561,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8561,21 +8575,21 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B251">
         <v>0</v>
       </c>
       <c r="C251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8589,7 +8603,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8603,7 +8617,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8617,7 +8631,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8640,12 +8654,12 @@
         <v>1</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9555,7 +9569,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9569,7 +9583,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9583,7 +9597,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9597,7 +9611,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9611,7 +9625,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9625,7 +9639,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -9639,7 +9653,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -9653,7 +9667,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -9667,7 +9681,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -9681,7 +9695,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -9695,21 +9709,35 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B332">
-        <v>0</v>
-      </c>
-      <c r="C332">
-        <v>1</v>
-      </c>
-      <c r="D332">
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+      <c r="D333">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D332"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D333"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D333"/>
+  <dimension ref="A1:D334"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>771</v>
+        <v>785</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +436,7 @@
         <v>311</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>265</v>
@@ -475,7 +475,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -545,13 +545,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -702,10 +702,10 @@
         <v>17</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1956,21 +1956,21 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>treinaadorrafael</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,13 +2026,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2040,41 +2040,41 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -2250,35 +2250,35 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,13 +2320,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,35 +2628,35 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,13 +3370,13 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -3384,13 +3384,13 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,13 +3636,13 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C232">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -3664,21 +3664,21 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D234">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -3692,21 +3692,21 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -3720,21 +3720,21 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,13 +3762,13 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,21 +3804,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,21 +3846,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3874,21 +3874,21 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
       <c r="C249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,21 +3916,21 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B252">
         <v>0</v>
       </c>
       <c r="C252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -3995,12 +3995,12 @@
         <v>1</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,28 +5050,42 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B333">
-        <v>0</v>
-      </c>
-      <c r="C333">
-        <v>1</v>
-      </c>
-      <c r="D333">
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+      <c r="D334">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D333"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D334"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D333"/>
+  <dimension ref="A1:D334"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5092,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>771</v>
+        <v>785</v>
       </c>
     </row>
     <row r="3">
@@ -5109,7 +5123,7 @@
         <v>311</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>265</v>
@@ -5148,7 +5162,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5176,13 +5190,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -5218,13 +5232,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -5375,10 +5389,10 @@
         <v>17</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -6629,21 +6643,21 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>treinaadorrafael</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6657,13 +6671,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6671,13 +6685,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6685,7 +6699,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6699,13 +6713,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -6713,41 +6727,41 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -6755,7 +6769,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6769,7 +6783,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6783,7 +6797,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6797,7 +6811,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6811,7 +6825,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6825,7 +6839,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6839,7 +6853,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6853,7 +6867,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6867,7 +6881,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6881,7 +6895,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6895,7 +6909,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6909,13 +6923,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -6923,35 +6937,35 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6965,7 +6979,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6979,7 +6993,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6993,13 +7007,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -7007,7 +7021,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -7021,7 +7035,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7035,7 +7049,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7049,7 +7063,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7063,7 +7077,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7077,7 +7091,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7091,7 +7105,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7105,7 +7119,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7119,7 +7133,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7133,7 +7147,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7147,7 +7161,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7161,7 +7175,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7175,7 +7189,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7189,7 +7203,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7203,7 +7217,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7217,7 +7231,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7231,7 +7245,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7245,7 +7259,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7259,7 +7273,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7273,7 +7287,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7287,7 +7301,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7301,35 +7315,35 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7343,7 +7357,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7357,7 +7371,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7371,7 +7385,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7385,7 +7399,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7399,7 +7413,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7413,7 +7427,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7427,7 +7441,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7441,7 +7455,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7455,7 +7469,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7469,7 +7483,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7483,7 +7497,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7497,7 +7511,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7511,7 +7525,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7525,7 +7539,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7539,7 +7553,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7553,7 +7567,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7567,7 +7581,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7581,7 +7595,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7595,7 +7609,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7609,7 +7623,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7623,7 +7637,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7637,7 +7651,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7651,7 +7665,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7665,7 +7679,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7679,7 +7693,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7693,7 +7707,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7707,7 +7721,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7721,7 +7735,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7735,7 +7749,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7749,7 +7763,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7763,7 +7777,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7777,7 +7791,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7791,7 +7805,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7805,7 +7819,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7819,7 +7833,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7847,7 +7861,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7861,7 +7875,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7875,7 +7889,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7889,7 +7903,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7903,7 +7917,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7917,7 +7931,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7931,7 +7945,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7973,7 +7987,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7987,7 +8001,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -8001,7 +8015,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -8015,7 +8029,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -8029,7 +8043,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -8043,13 +8057,13 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -8057,13 +8071,13 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -8071,7 +8085,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -8085,7 +8099,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -8099,7 +8113,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -8127,7 +8141,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -8141,7 +8155,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8155,7 +8169,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8169,7 +8183,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8183,7 +8197,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8197,7 +8211,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8211,7 +8225,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8225,7 +8239,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -8239,7 +8253,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -8253,7 +8267,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -8267,7 +8281,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -8281,7 +8295,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -8309,13 +8323,13 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C232">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -8323,7 +8337,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8337,21 +8351,21 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D234">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8365,21 +8379,21 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8393,21 +8407,21 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8421,7 +8435,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8435,13 +8449,13 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8463,7 +8477,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8477,21 +8491,21 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8505,7 +8519,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8519,21 +8533,21 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8547,21 +8561,21 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
       <c r="C249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8575,7 +8589,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8589,21 +8603,21 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B252">
         <v>0</v>
       </c>
       <c r="C252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8617,7 +8631,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8668,12 +8682,12 @@
         <v>1</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9555,7 +9569,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9569,7 +9583,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9583,7 +9597,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9597,7 +9611,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9611,7 +9625,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9625,7 +9639,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9639,7 +9653,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -9653,7 +9667,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -9667,7 +9681,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -9681,7 +9695,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -9695,7 +9709,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -9709,7 +9723,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -9723,21 +9737,35 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B333">
-        <v>0</v>
-      </c>
-      <c r="C333">
-        <v>1</v>
-      </c>
-      <c r="D333">
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+      <c r="D334">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D333"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D334"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>785</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3">
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -528,30 +528,30 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>anaaj_camargo</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>rm.nicki</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -576,10 +576,10 @@
         <v>37</v>
       </c>
       <c r="C13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -780,72 +780,72 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>eliassilverio</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>cjrnavalha</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>tabajaraharu</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
         <v>6</v>
-      </c>
-      <c r="C31">
-        <v>11</v>
-      </c>
-      <c r="D31">
-        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>hugo7jj</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -5106,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1024</v>
+        <v>1033</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>785</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3">
@@ -5190,13 +5190,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -5215,30 +5215,30 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>anaaj_camargo</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>rm.nicki</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -5263,10 +5263,10 @@
         <v>37</v>
       </c>
       <c r="C13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -5467,72 +5467,72 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>eliassilverio</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>cjrnavalha</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>tabajaraharu</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
         <v>6</v>
-      </c>
-      <c r="C31">
-        <v>11</v>
-      </c>
-      <c r="D31">
-        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>hugo7jj</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -531,7 +531,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -545,7 +545,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -573,13 +573,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>28</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -699,13 +699,13 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -738,55 +738,55 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>alvesmidih</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B26">
         <v>15</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>tiwimma</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
         <v>5</v>
-      </c>
-      <c r="D27">
-        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>hugo7jj</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -867,7 +867,7 @@
         <v>_beegomes_</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -5106,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="3">
@@ -5120,13 +5120,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -5134,13 +5134,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -5204,7 +5204,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -5232,7 +5232,7 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -5260,13 +5260,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>28</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -5386,13 +5386,13 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -5425,55 +5425,55 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>alvesmidih</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B26">
         <v>15</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>tiwimma</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
         <v>5</v>
-      </c>
-      <c r="D27">
-        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>hugo7jj</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -5554,7 +5554,7 @@
         <v>_beegomes_</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>795</v>
+        <v>809</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -486,30 +486,30 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pablofiorindi</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rpsantos_mma</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B8">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -702,7 +702,7 @@
         <v>18</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22">
         <v>14</v>
@@ -5106,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>795</v>
+        <v>809</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -5173,30 +5173,30 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pablofiorindi</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rpsantos_mma</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B8">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -5204,13 +5204,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -5218,13 +5218,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -5389,7 +5389,7 @@
         <v>18</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22">
         <v>14</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1048</v>
+        <v>1062</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>809</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -475,41 +475,41 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rpsantos_mma</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>pablofiorindi</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -668,30 +668,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B20">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -5106,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1048</v>
+        <v>1062</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>809</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -5162,41 +5162,41 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rpsantos_mma</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>pablofiorindi</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -5218,13 +5218,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -5355,30 +5355,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B20">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>823</v>
+        <v>831</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>32</v>
@@ -699,13 +699,13 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -850,13 +850,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>tawanregismma</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>_beegomes_</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B34">
         <v>7</v>
@@ -873,21 +873,21 @@
         <v>1</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B35">
         <v>7</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -5106,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>823</v>
+        <v>831</v>
       </c>
     </row>
     <row r="3">
@@ -5120,13 +5120,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4">
@@ -5176,13 +5176,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -5263,7 +5263,7 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>32</v>
@@ -5386,13 +5386,13 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -5537,13 +5537,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>tawanregismma</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>_beegomes_</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B34">
         <v>7</v>
@@ -5560,21 +5560,21 @@
         <v>1</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B35">
         <v>7</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -461,7 +461,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -724,30 +724,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>leandro._bjj</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B24">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>hugo7jj</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -5106,13 +5106,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3">
@@ -5120,7 +5120,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -5148,7 +5148,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -5176,7 +5176,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -5218,13 +5218,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -5411,30 +5411,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>leandro._bjj</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B24">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>hugo7jj</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B25">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:D335"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -1970,21 +1970,21 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -2054,41 +2054,41 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,13 +2250,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -2264,35 +2264,35 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,35 +2642,35 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,13 +3384,13 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -3398,13 +3398,13 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,13 +3650,13 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C233">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -3678,21 +3678,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D235">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -3706,21 +3706,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -3734,21 +3734,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -3818,21 +3818,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -3860,21 +3860,21 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -3888,21 +3888,21 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
       <c r="C250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3930,21 +3930,21 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B253">
         <v>0</v>
       </c>
       <c r="C253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4009,12 +4009,12 @@
         <v>1</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,28 +5064,42 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B334">
-        <v>0</v>
-      </c>
-      <c r="C334">
-        <v>1</v>
-      </c>
-      <c r="D334">
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+      <c r="D335">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D334"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D335"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:D335"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5148,13 +5162,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -6657,21 +6671,21 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6685,13 +6699,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6699,13 +6713,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -6713,7 +6727,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6727,13 +6741,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -6741,41 +6755,41 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>guiiviieira_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -6783,7 +6797,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6797,7 +6811,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6811,7 +6825,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6825,7 +6839,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -6839,7 +6853,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6853,7 +6867,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6867,7 +6881,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6881,7 +6895,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6895,7 +6909,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6909,7 +6923,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6923,7 +6937,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6937,13 +6951,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -6951,35 +6965,35 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -6993,7 +7007,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -7007,7 +7021,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -7021,13 +7035,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>tonketjudes</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -7035,7 +7049,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7049,7 +7063,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7063,7 +7077,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7077,7 +7091,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7091,7 +7105,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7105,7 +7119,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7119,7 +7133,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7133,7 +7147,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7147,7 +7161,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7161,7 +7175,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7175,7 +7189,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7189,7 +7203,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7203,7 +7217,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7217,7 +7231,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7231,7 +7245,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7245,7 +7259,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7259,7 +7273,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7273,7 +7287,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7287,7 +7301,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7301,7 +7315,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7315,7 +7329,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7329,35 +7343,35 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7371,7 +7385,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7385,7 +7399,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7399,7 +7413,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7413,7 +7427,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7427,7 +7441,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7441,7 +7455,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7455,7 +7469,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7469,7 +7483,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7483,7 +7497,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7497,7 +7511,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7511,7 +7525,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7525,7 +7539,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7539,7 +7553,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7553,7 +7567,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7567,7 +7581,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7581,7 +7595,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7595,7 +7609,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7609,7 +7623,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7623,7 +7637,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7637,7 +7651,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7651,7 +7665,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7665,7 +7679,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7679,7 +7693,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7693,7 +7707,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7707,7 +7721,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7721,7 +7735,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7735,7 +7749,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7749,7 +7763,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7763,7 +7777,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7777,7 +7791,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7791,7 +7805,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7805,7 +7819,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7819,7 +7833,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7847,7 +7861,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7861,7 +7875,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7875,7 +7889,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7889,7 +7903,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7903,7 +7917,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7917,7 +7931,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7931,7 +7945,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7973,7 +7987,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7987,7 +8001,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -8001,7 +8015,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -8015,7 +8029,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -8029,7 +8043,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -8043,7 +8057,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -8057,7 +8071,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -8071,13 +8085,13 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -8085,13 +8099,13 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -8099,7 +8113,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -8127,7 +8141,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -8141,7 +8155,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -8155,7 +8169,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -8169,7 +8183,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -8183,7 +8197,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -8197,7 +8211,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -8211,7 +8225,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -8225,7 +8239,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -8239,7 +8253,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -8253,7 +8267,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -8267,7 +8281,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -8281,7 +8295,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -8309,7 +8323,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -8323,7 +8337,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -8337,13 +8351,13 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C233">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -8351,7 +8365,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8365,21 +8379,21 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D235">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8393,21 +8407,21 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8421,21 +8435,21 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>dayanaa1511</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8463,13 +8477,13 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>vanessamelomma</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -8477,7 +8491,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8491,7 +8505,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8505,21 +8519,21 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8533,7 +8547,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8547,21 +8561,21 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8575,21 +8589,21 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
       <c r="C250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8603,7 +8617,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8617,21 +8631,21 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B253">
         <v>0</v>
       </c>
       <c r="C253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8696,12 +8710,12 @@
         <v>1</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>esteticaluharruda</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -9555,7 +9569,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -9569,7 +9583,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -9583,7 +9597,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -9597,7 +9611,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -9611,7 +9625,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -9625,7 +9639,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -9639,7 +9653,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -9653,7 +9667,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -9667,7 +9681,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -9681,7 +9695,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -9695,7 +9709,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -9709,7 +9723,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -9723,7 +9737,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -9737,7 +9751,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -9751,21 +9765,35 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
         <v>armysenju</v>
       </c>
-      <c r="B334">
-        <v>0</v>
-      </c>
-      <c r="C334">
-        <v>1</v>
-      </c>
-      <c r="D334">
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+      <c r="D335">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D334"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D335"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -5099,7 +5099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D335"/>
+  <dimension ref="A1:D289"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1071</v>
+        <v>1049</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>832</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5134,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>267</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
@@ -5148,13 +5148,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -5190,13 +5190,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -5204,7 +5204,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -5277,7 +5277,7 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>32</v>
@@ -5369,30 +5369,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C20">
-        <v>114</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
@@ -5411,13 +5411,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gra_jpereira</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>12</v>
@@ -5425,30 +5425,30 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>hugo7jj</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>leandro._bjj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B25">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -5481,30 +5481,30 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>eliassilverio</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B29">
         <v>10</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -5540,7 +5540,7 @@
         <v>tabajaraharu</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>11</v>
@@ -5551,27 +5551,27 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>tawanregismma</v>
+        <v>maxgandra</v>
       </c>
       <c r="B34">
         <v>7</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -5579,69 +5579,69 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>_beegomes_</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>rrafaelins</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>italothearcher</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>italothearcher</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>vndcardoso</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -5649,55 +5649,55 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>juniordiasmma</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>gdazuera</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>enzoferrari680</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>paxlucta</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -5705,83 +5705,83 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>eolucasrosa</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>dagestan0920</v>
+        <v>gdazuera</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>paxlucta</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>badboykillermma</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>_.maduoliveira_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -5789,13 +5789,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -5803,27 +5803,27 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>karen.ottoni</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>glm.barbosa</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>2</v>
@@ -5831,83 +5831,83 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marcelogabrielmma</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53">
         <v>3</v>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
       <c r="D53">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>_oliveira09_</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>edebetim_</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>gabrielsouzamma</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>salost.ofc</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ravenrodriguez___</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B58">
         <v>4</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -5915,97 +5915,97 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>fabinho_falcao_</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ailinperezufc</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>mah__vergueiro</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>marcos_tailandess</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>lipe.ftt</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fau_gfs</v>
+        <v>febrancatti</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>shawlin13oficial</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -6013,21 +6013,21 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>eduardorodrigrs</v>
+        <v>reifernandes</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>febrancatti</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -6055,35 +6055,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>dogodoyfoto</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>reifernandes</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>daniel_dias_214</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -6097,63 +6097,63 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>alexsandra_kairos</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>f.luan_11</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>vitorpetrino</v>
+        <v>edebetim_</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>jcchagas_</v>
+        <v>s__simone__</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -6162,15 +6162,15 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>anderson.logan.35</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -6181,44 +6181,44 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>marifferreirac</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>odeivisoncardoso</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>maca.mariotti</v>
+        <v>ruangzk</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -6229,7 +6229,7 @@
         <v>1</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -6237,27 +6237,27 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>s__simone__</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>kaua_limaofc</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -6265,77 +6265,77 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>clouddhidden</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lucascardosol__</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ruangzk</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>washington_cassisno</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ismaeldaniell</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>douglasipvr_mma</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -6344,32 +6344,32 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>tassiogiloficial</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>vnciuss__df</v>
+        <v>joegam3r</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>jhee_dias</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -6391,13 +6391,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>albertoleandromoco</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -6405,41 +6405,41 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>pauloserrati</v>
+        <v>orafao1</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fredoctmma</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -6447,13 +6447,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>diegopaivajj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -6461,13 +6461,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fabaotipster</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -6475,63 +6475,63 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>joegam3r</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mimuniz.bjj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>orafao1</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fabi.godooy</v>
+        <v>graalino</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>leobahiamma</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -6559,7 +6559,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -6573,77 +6573,77 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>heltoncm2002</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>raelduraes</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>mineirinho_jj</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>graalino</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>lopesbrunao</v>
+        <v>030sami</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6652,18 +6652,18 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ninjatheorist</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -6671,27 +6671,27 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>pedrinhosbjj</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>treinaadorrafael</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -6699,13 +6699,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fernando.mma</v>
+        <v>cshigueo</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -6713,13 +6713,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -6727,13 +6727,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -6741,13 +6741,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>fagnerosensei</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>030sami</v>
+        <v>mttsm._</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6769,27 +6769,27 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>benjafloripabjj</v>
+        <v>gildojiu</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>cshigueo</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6825,13 +6825,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -6839,13 +6839,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>emerson_lucaszx</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>danni_goncalves12</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -6867,7 +6867,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>mttsm._</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>andrealvess02</v>
+        <v>pdfiv</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>gildojiu</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>kawannsennast</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>yurimartins1_</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>matheusteodoro_1</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6965,13 +6965,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>kael_lyto</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -6979,27 +6979,27 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>cristianpsicologo</v>
+        <v>anahangelica</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>juanx.pontes</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -7007,13 +7007,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>select_from_joao</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -7021,13 +7021,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>yeslifeacademia</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -7035,13 +7035,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>ojaimerocha</v>
+        <v>codasqueves</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -7049,7 +7049,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>tonketjudes</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>_eliasffx</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>pdfiv</v>
+        <v>davicorbella</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>mariaraimundad940</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>gabesantos.13</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>euvitormirandaa</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>thompsonborralho</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>frankikolimabjj</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7161,21 +7161,21 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>alerrandrojj</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>anahangelica</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>minotaurinho</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>lara.rpr</v>
+        <v>eliandropires</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>codasqueves</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>yan_touro.7766</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>carolinne.xwp</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>davicorbella</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>artemio_bjj</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>katiaecarreraf</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>geraldocnetomma</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7357,21 +7357,21 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>pedro_pavin_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C162">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D162">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>xavyeroficial</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>maryanagandra</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>eliandropires</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>charlesanthony2466</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>draanapaulaponceano</v>
+        <v>pietroshz</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>saj_photo_miami</v>
+        <v>___neller</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>alternativaremocoes</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>benivalentinn</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>pativinisf</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>navarro_9430</v>
+        <v>judadany</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>_puroosso88</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>_rayysp</v>
+        <v>_fernunes</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>cami.terra_</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>gabicardoson</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>martta.mariah</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>wlt_miguel</v>
+        <v>flazuera14</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>jaonevesz</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>pietroshz</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>___neller</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>_bety_marcal</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>guilhermeefelix__</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>pativinisf</v>
+        <v>muricunha</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>judadany</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>andre_alcausa</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>_fernunes</v>
+        <v>__bielgg</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>aloirmarcal</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7749,7 +7749,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>gilberto_7606</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>flazuera14</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>camii_bonfim</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>danlouiz.jj</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>gabriel_trevelin</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>y.arthur_01</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7861,7 +7861,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>muricunha</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7875,7 +7875,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>victorhenriquebjj</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>_lsanchess_</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>__bielgg</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7917,13 +7917,13 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>mr__rlk01</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>vitor_buck</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>fran.ruys</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>wesley_bjjvc</v>
+        <v>andrejetx</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>sambagabrieloficial</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>peacegrappler</v>
+        <v>turmanmma</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -8015,7 +8015,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>aliferpaulo_</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -8029,13 +8029,13 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>_alcantara.bru</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -8043,55 +8043,55 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>cesar.boanerges</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>alexandreconsentino</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -8099,13 +8099,13 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>rafaela_duaartee</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B215">
         <v>0</v>
       </c>
       <c r="C215">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -8113,27 +8113,27 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>andre.legendre.10</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -8141,69 +8141,69 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>phillipe.harry</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>andrejetx</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>leandro_motiv4</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>olga.oliveira013</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -8211,13 +8211,13 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>leosacraa</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -8225,13 +8225,13 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>gutocriativo</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -8239,41 +8239,41 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>igorfso_</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>coutz11</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>lay_roqs</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -8281,13 +8281,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>bigjota.artist</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -8295,27 +8295,27 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>mth_fernandes031</v>
+        <v>4lissson</v>
       </c>
       <c r="B230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -8323,55 +8323,55 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>ommariotti</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>turmanmma</v>
+        <v>brodschack_</v>
       </c>
       <c r="B232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>gustavomohallem</v>
+        <v>_vpft</v>
       </c>
       <c r="B233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>marinealcausa</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -8379,13 +8379,13 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>emersonriosmma</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D235">
         <v>0</v>
@@ -8393,41 +8393,41 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>luizcosta_mma</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>giulia.fasolato</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>michelle_mirele</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D238">
         <v>0</v>
@@ -8435,13 +8435,13 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>danielfranzesilva</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D239">
         <v>0</v>
@@ -8449,49 +8449,49 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>ednilsonkaicai</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>vanemessina</v>
       </c>
       <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>dayanaa1511</v>
+        <v>dadwillians</v>
       </c>
       <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>vanessamelomma</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8500,12 +8500,12 @@
         <v>1</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>leonardopateira</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8514,12 +8514,12 @@
         <v>1</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>rahikikhalid</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8528,18 +8528,18 @@
         <v>1</v>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>manumito.oficial</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -8547,13 +8547,13 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>carlosnoelblack</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247">
         <v>0</v>
@@ -8561,13 +8561,13 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>dandraco_</v>
       </c>
       <c r="B248">
         <v>0</v>
       </c>
       <c r="C248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -8575,7 +8575,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>lokomemo_protetores</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8584,12 +8584,12 @@
         <v>1</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>coutz11</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8598,18 +8598,18 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>orlando_alfa09</v>
+        <v>tpapereira</v>
       </c>
       <c r="B251">
         <v>0</v>
       </c>
       <c r="C251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -8617,13 +8617,13 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>vitorshowman</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B252">
         <v>0</v>
       </c>
       <c r="C252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -8631,13 +8631,13 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>4lissson</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B253">
         <v>0</v>
       </c>
       <c r="C253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>danilofernandescf</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8654,12 +8654,12 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>bryandazuera</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8668,12 +8668,12 @@
         <v>1</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>ommariotti</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8682,12 +8682,12 @@
         <v>1</v>
       </c>
       <c r="D256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>brodschack_</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8696,12 +8696,12 @@
         <v>1</v>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>_vpft</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8710,12 +8710,12 @@
         <v>1</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>doraasivla</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>helenaseveribjj</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8743,7 +8743,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>_kainanlima</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8757,7 +8757,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>jimmy_indioap</v>
+        <v>caioparangole</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>omar_alneaimi</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8785,7 +8785,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>victor_brunopersonal</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -8799,7 +8799,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>motumbo_team</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -8813,7 +8813,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>vanemessina</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -8827,7 +8827,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>dadwillians</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -8841,7 +8841,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>thalytabjj</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -8869,7 +8869,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>esteticaluharruda</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>chubotaru_lilu</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>eusoufernandosaito</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -8911,7 +8911,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>dandraco_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -8939,7 +8939,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>sejamotivadorofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -8953,7 +8953,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>tpapereira</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>kfcampeoes</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -8981,7 +8981,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>herrickmarinho</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -8995,7 +8995,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>rafaelcmjj</v>
+        <v>alineanne_</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>cristianomarcello</v>
+        <v>julckreis</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -9023,7 +9023,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>_gabrielpego</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -9037,7 +9037,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>taylor_71kg</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -9051,7 +9051,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>doraasivla</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -9079,7 +9079,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>pe.mirandas</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -9093,7 +9093,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>leaoanaalice</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>caioparangole</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -9121,7 +9121,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>sabrinaalsilva</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -9135,7 +9135,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>armysenju</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -9144,656 +9144,12 @@
         <v>1</v>
       </c>
       <c r="D289">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="str">
-        <v>eglaudiomma</v>
-      </c>
-      <c r="B290">
-        <v>0</v>
-      </c>
-      <c r="C290">
-        <v>1</v>
-      </c>
-      <c r="D290">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="str">
-        <v>strong_stg_oficial</v>
-      </c>
-      <c r="B291">
-        <v>0</v>
-      </c>
-      <c r="C291">
-        <v>1</v>
-      </c>
-      <c r="D291">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="str">
-        <v>ricardotofanello</v>
-      </c>
-      <c r="B292">
-        <v>0</v>
-      </c>
-      <c r="C292">
-        <v>1</v>
-      </c>
-      <c r="D292">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="str">
-        <v>taporondebruno</v>
-      </c>
-      <c r="B293">
-        <v>0</v>
-      </c>
-      <c r="C293">
-        <v>1</v>
-      </c>
-      <c r="D293">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="str">
-        <v>anamatias.m</v>
-      </c>
-      <c r="B294">
-        <v>0</v>
-      </c>
-      <c r="C294">
-        <v>1</v>
-      </c>
-      <c r="D294">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="str">
-        <v>claudio_marchese_7</v>
-      </c>
-      <c r="B295">
-        <v>0</v>
-      </c>
-      <c r="C295">
-        <v>1</v>
-      </c>
-      <c r="D295">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="str">
-        <v>1000ton_n</v>
-      </c>
-      <c r="B296">
-        <v>0</v>
-      </c>
-      <c r="C296">
-        <v>1</v>
-      </c>
-      <c r="D296">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="str">
-        <v>paulo.titoo</v>
-      </c>
-      <c r="B297">
-        <v>0</v>
-      </c>
-      <c r="C297">
-        <v>1</v>
-      </c>
-      <c r="D297">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="str">
-        <v>vitorcosta_mma</v>
-      </c>
-      <c r="B298">
-        <v>0</v>
-      </c>
-      <c r="C298">
-        <v>1</v>
-      </c>
-      <c r="D298">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="str">
-        <v>couragemma</v>
-      </c>
-      <c r="B299">
-        <v>0</v>
-      </c>
-      <c r="C299">
-        <v>1</v>
-      </c>
-      <c r="D299">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="str">
-        <v>romulerasilva</v>
-      </c>
-      <c r="B300">
-        <v>0</v>
-      </c>
-      <c r="C300">
-        <v>1</v>
-      </c>
-      <c r="D300">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="str">
-        <v>edergama.mma</v>
-      </c>
-      <c r="B301">
-        <v>0</v>
-      </c>
-      <c r="C301">
-        <v>1</v>
-      </c>
-      <c r="D301">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="str">
-        <v>alineanne_</v>
-      </c>
-      <c r="B302">
-        <v>0</v>
-      </c>
-      <c r="C302">
-        <v>1</v>
-      </c>
-      <c r="D302">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="str">
-        <v>julckreis</v>
-      </c>
-      <c r="B303">
-        <v>0</v>
-      </c>
-      <c r="C303">
-        <v>1</v>
-      </c>
-      <c r="D303">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="str">
-        <v>andreza.thais.1</v>
-      </c>
-      <c r="B304">
-        <v>0</v>
-      </c>
-      <c r="C304">
-        <v>1</v>
-      </c>
-      <c r="D304">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="str">
-        <v>benicius_edu</v>
-      </c>
-      <c r="B305">
-        <v>0</v>
-      </c>
-      <c r="C305">
-        <v>1</v>
-      </c>
-      <c r="D305">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="str">
-        <v>nataliaemanuela.personal</v>
-      </c>
-      <c r="B306">
-        <v>0</v>
-      </c>
-      <c r="C306">
-        <v>1</v>
-      </c>
-      <c r="D306">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="str">
-        <v>michele_mixa</v>
-      </c>
-      <c r="B307">
-        <v>0</v>
-      </c>
-      <c r="C307">
-        <v>1</v>
-      </c>
-      <c r="D307">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="str">
-        <v>joaolauar_</v>
-      </c>
-      <c r="B308">
-        <v>0</v>
-      </c>
-      <c r="C308">
-        <v>1</v>
-      </c>
-      <c r="D308">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="str">
-        <v>igorbrasileiro01</v>
-      </c>
-      <c r="B309">
-        <v>0</v>
-      </c>
-      <c r="C309">
-        <v>1</v>
-      </c>
-      <c r="D309">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="str">
-        <v>felipeocalmon</v>
-      </c>
-      <c r="B310">
-        <v>0</v>
-      </c>
-      <c r="C310">
-        <v>1</v>
-      </c>
-      <c r="D310">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="str">
-        <v>rejr_mma</v>
-      </c>
-      <c r="B311">
-        <v>0</v>
-      </c>
-      <c r="C311">
-        <v>1</v>
-      </c>
-      <c r="D311">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="str">
-        <v>deivssonmanin</v>
-      </c>
-      <c r="B312">
-        <v>0</v>
-      </c>
-      <c r="C312">
-        <v>1</v>
-      </c>
-      <c r="D312">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="str">
-        <v>andrey_m_s_</v>
-      </c>
-      <c r="B313">
-        <v>0</v>
-      </c>
-      <c r="C313">
-        <v>1</v>
-      </c>
-      <c r="D313">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="str">
-        <v>vidaldanin</v>
-      </c>
-      <c r="B314">
-        <v>0</v>
-      </c>
-      <c r="C314">
-        <v>1</v>
-      </c>
-      <c r="D314">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="str">
-        <v>barbaracontadora</v>
-      </c>
-      <c r="B315">
-        <v>0</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="str">
-        <v>natalves5</v>
-      </c>
-      <c r="B316">
-        <v>0</v>
-      </c>
-      <c r="C316">
-        <v>1</v>
-      </c>
-      <c r="D316">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="str">
-        <v>marlon_bodybuilding</v>
-      </c>
-      <c r="B317">
-        <v>0</v>
-      </c>
-      <c r="C317">
-        <v>1</v>
-      </c>
-      <c r="D317">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="str">
-        <v>boradepodcastoficial</v>
-      </c>
-      <c r="B318">
-        <v>0</v>
-      </c>
-      <c r="C318">
-        <v>1</v>
-      </c>
-      <c r="D318">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="str">
-        <v>audizioandrade</v>
-      </c>
-      <c r="B319">
-        <v>0</v>
-      </c>
-      <c r="C319">
-        <v>1</v>
-      </c>
-      <c r="D319">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="str">
-        <v>isadoragolimpio</v>
-      </c>
-      <c r="B320">
-        <v>0</v>
-      </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="str">
-        <v>dudu.acabamentos</v>
-      </c>
-      <c r="B321">
-        <v>0</v>
-      </c>
-      <c r="C321">
-        <v>1</v>
-      </c>
-      <c r="D321">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="str">
-        <v>katlembrenda</v>
-      </c>
-      <c r="B322">
-        <v>0</v>
-      </c>
-      <c r="C322">
-        <v>1</v>
-      </c>
-      <c r="D322">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="str">
-        <v>aline.amaral21</v>
-      </c>
-      <c r="B323">
-        <v>0</v>
-      </c>
-      <c r="C323">
-        <v>1</v>
-      </c>
-      <c r="D323">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="str">
-        <v>tamysregina</v>
-      </c>
-      <c r="B324">
-        <v>0</v>
-      </c>
-      <c r="C324">
-        <v>1</v>
-      </c>
-      <c r="D324">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="str">
-        <v>guilhermews1994</v>
-      </c>
-      <c r="B325">
-        <v>0</v>
-      </c>
-      <c r="C325">
-        <v>1</v>
-      </c>
-      <c r="D325">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="str">
-        <v>percepcar</v>
-      </c>
-      <c r="B326">
-        <v>0</v>
-      </c>
-      <c r="C326">
-        <v>1</v>
-      </c>
-      <c r="D326">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="str">
-        <v>kevin.mota95</v>
-      </c>
-      <c r="B327">
-        <v>0</v>
-      </c>
-      <c r="C327">
-        <v>1</v>
-      </c>
-      <c r="D327">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="str">
-        <v>_marcos_.71</v>
-      </c>
-      <c r="B328">
-        <v>0</v>
-      </c>
-      <c r="C328">
-        <v>1</v>
-      </c>
-      <c r="D328">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="str">
-        <v>douglas_vitor8</v>
-      </c>
-      <c r="B329">
-        <v>0</v>
-      </c>
-      <c r="C329">
-        <v>1</v>
-      </c>
-      <c r="D329">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="str">
-        <v>gemeaslauraebrenda</v>
-      </c>
-      <c r="B330">
-        <v>0</v>
-      </c>
-      <c r="C330">
-        <v>1</v>
-      </c>
-      <c r="D330">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="str">
-        <v>raulcarvalho1010</v>
-      </c>
-      <c r="B331">
-        <v>0</v>
-      </c>
-      <c r="C331">
-        <v>1</v>
-      </c>
-      <c r="D331">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="str">
-        <v>roginbrito</v>
-      </c>
-      <c r="B332">
-        <v>0</v>
-      </c>
-      <c r="C332">
-        <v>1</v>
-      </c>
-      <c r="D332">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="str">
-        <v>meirelesmma</v>
-      </c>
-      <c r="B333">
-        <v>0</v>
-      </c>
-      <c r="C333">
-        <v>1</v>
-      </c>
-      <c r="D333">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="str">
-        <v>dvlucc2k26_</v>
-      </c>
-      <c r="B334">
-        <v>0</v>
-      </c>
-      <c r="C334">
-        <v>1</v>
-      </c>
-      <c r="D334">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="str">
-        <v>armysenju</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-      <c r="C335">
-        <v>1</v>
-      </c>
-      <c r="D335">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D335"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D289"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -576,10 +576,10 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -710,27 +710,27 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gra_jpereira</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>hugo7jj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5134,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
@@ -5204,7 +5204,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -5277,10 +5277,10 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -5414,13 +5414,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3">
@@ -436,10 +436,10 @@
         <v>315</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">
@@ -668,58 +668,58 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>god.motivacao</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>cleyton_jesuss</v>
+        <v>aline.r15</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>hugo7jj</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B23">
         <v>20</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="3">
@@ -5137,10 +5137,10 @@
         <v>280</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
@@ -5369,30 +5369,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>aline.r15</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B21">
+        <v>22</v>
+      </c>
+      <c r="C21">
         <v>6</v>
       </c>
-      <c r="C21">
-        <v>113</v>
-      </c>
       <c r="D21">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -5400,27 +5400,27 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>hugo7jj</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="3">
@@ -436,10 +436,10 @@
         <v>315</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -1298,7 +1298,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -1307,12 +1307,12 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B67">
         <v>2</v>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1354,13 +1354,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -1368,35 +1368,35 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -1410,27 +1410,27 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -1438,21 +1438,21 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1466,91 +1466,91 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>adriano.trator</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1578,21 +1578,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -1606,69 +1606,69 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -1676,13 +1676,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B92">
         <v>2</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -1690,35 +1690,35 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -1732,7 +1732,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -1741,18 +1741,18 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -1760,13 +1760,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -1774,21 +1774,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -1830,21 +1830,21 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ninjatheorist</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3">
@@ -5137,10 +5137,10 @@
         <v>280</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -5204,13 +5204,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -5943,7 +5943,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -5952,12 +5952,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -5971,7 +5971,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -5999,13 +5999,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -6013,35 +6013,35 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -6055,35 +6055,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>f.luan_11</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -6097,77 +6097,77 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>odeivisoncardoso</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>edebetim_</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>s__simone__</v>
+        <v>edebetim_</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -6195,21 +6195,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -6223,13 +6223,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>adriano.trator</v>
+        <v>ruangzk</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -6237,69 +6237,69 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>washington_cassisno</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -6321,27 +6321,27 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fredoctmma</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabaotipster</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -6363,21 +6363,21 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B92">
         <v>2</v>
@@ -6391,35 +6391,35 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>diegopaivajj</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>orafao1</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -6433,21 +6433,21 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6475,7 +6475,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>raelduraes</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>graalino</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6531,7 +6531,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ninjatheorist</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B104">
         <v>1</v>

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -436,10 +436,10 @@
         <v>315</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -654,30 +654,30 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>hugo7jj</v>
+        <v>combintel</v>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -5137,10 +5137,10 @@
         <v>280</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
@@ -5355,30 +5355,30 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>combintel</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B19">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>hugo7jj</v>
+        <v>combintel</v>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -5099,7 +5099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D289"/>
+  <dimension ref="A1:D263"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5134,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>236</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
@@ -5148,13 +5148,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -5190,13 +5190,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -5204,13 +5204,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -5271,44 +5271,44 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B13">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ronemayanmorais</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>bellsouza816</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -5400,7 +5400,7 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -5414,13 +5414,13 @@
         <v>god.motivacao</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>113</v>
       </c>
       <c r="D23">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -5445,10 +5445,10 @@
         <v>17</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -5481,13 +5481,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>eliassilverio</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B28">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -5495,58 +5495,58 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pedromadeira.s</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>cjrnavalha</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>tabajaraharu</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
         <v>5</v>
-      </c>
-      <c r="C32">
-        <v>11</v>
-      </c>
-      <c r="D32">
-        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -5607,86 +5607,86 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>italothearcher</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>juniordiasmma</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>enzoferrari680</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>italothearcher</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>rrafaelins</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -5761,44 +5761,44 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>marcelogabrielmma</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B49">
         <v>3</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -5809,7 +5809,7 @@
         <v>4</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -6055,35 +6055,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>f.luan_11</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>vitorpetrino</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -6097,77 +6097,77 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>jcchagas_</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>anderson.logan.35</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>odeivisoncardoso</v>
+        <v>edebetim_</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74">
         <v>3</v>
-      </c>
-      <c r="D74">
-        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>maca.mariotti</v>
+        <v>s__simone__</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>edebetim_</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>s__simone__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -6181,41 +6181,41 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>kaua_limaofc</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>clouddhidden</v>
+        <v>ruangzk</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>lucascardosol__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -6223,49 +6223,49 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ruangzk</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>adriano.trator</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>washington_cassisno</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ismaeldaniell</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -6279,49 +6279,49 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>douglasipvr_mma</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>tassiogiloficial</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>vnciuss__df</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>jhee_dias</v>
+        <v>joegam3r</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -6335,41 +6335,41 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>albertoleandromoco</v>
+        <v>orafao1</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fredoctmma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>fabaotipster</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -6377,41 +6377,41 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>joegam3r</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>mimuniz.bjj</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>diegopaivajj</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -6419,35 +6419,35 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>orafao1</v>
+        <v>raelduraes</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>fabi.godooy</v>
+        <v>graalino</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>leobahiamma</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -6475,63 +6475,63 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>heltoncm2002</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>raelduraes</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>graalino</v>
+        <v>030sami</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -6540,18 +6540,18 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>lopesbrunao</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -6559,27 +6559,27 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>pedrinhosbjj</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>treinaadorrafael</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -6587,13 +6587,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>fernando.mma</v>
+        <v>cshigueo</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -6601,13 +6601,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -6615,13 +6615,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -6629,13 +6629,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fagnerosensei</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>030sami</v>
+        <v>mttsm._</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6657,27 +6657,27 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>benjafloripabjj</v>
+        <v>gildojiu</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>cshigueo</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>emerson_lucaszx</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>danni_goncalves12</v>
+        <v>pdfiv</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mttsm._</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>andrealvess02</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>gildojiu</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>kawannsennast</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>matheusteodoro_1</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6825,13 +6825,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>juanx.pontes</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -6839,13 +6839,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>yeslifeacademia</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -6853,21 +6853,21 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>tonketjudes</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>_eliasffx</v>
+        <v>anahangelica</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>pdfiv</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>mariaraimundad940</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>gabesantos.13</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>euvitormirandaa</v>
+        <v>codasqueves</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>thompsonborralho</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>frankikolimabjj</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>alerrandrojj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>anahangelica</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>minotaurinho</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>lara.rpr</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -7035,7 +7035,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>codasqueves</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -7049,21 +7049,21 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>yan_touro.7766</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>carolinne.xwp</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>davicorbella</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>eliandropires</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>artemio_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>katiaecarreraf</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>geraldocnetomma</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7161,21 +7161,21 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>pedro_pavin_</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>karen.ottoni</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>xavyeroficial</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>maryanagandra</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>eliandropires</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>charlesanthony2466</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>_rayysp</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>draanapaulaponceano</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>saj_photo_miami</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>alternativaremocoes</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>benivalentinn</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>navarro_9430</v>
+        <v>pietroshz</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>_puroosso88</v>
+        <v>___neller</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>_rayysp</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>cami.terra_</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>gabicardoson</v>
+        <v>pativinisf</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>martta.mariah</v>
+        <v>judadany</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>wlt_miguel</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>jaonevesz</v>
+        <v>_fernunes</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>pietroshz</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>___neller</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>_bety_marcal</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>guilhermeefelix__</v>
+        <v>flazuera14</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>pativinisf</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>judadany</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>andre_alcausa</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>_fernunes</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>aloirmarcal</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>gilberto_7606</v>
+        <v>muricunha</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>flazuera14</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>__bielgg</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>camii_bonfim</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>danlouiz.jj</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>gabriel_trevelin</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>y.arthur_01</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>muricunha</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>victorhenriquebjj</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>_lsanchess_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>__bielgg</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>mr__rlk01</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7749,13 +7749,13 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>vitor_buck</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>fran.ruys</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>wesley_bjjvc</v>
+        <v>turmanmma</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>sambagabrieloficial</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7819,13 +7819,13 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>peacegrappler</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -7833,41 +7833,41 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>aliferpaulo_</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>_alcantara.bru</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cesar.boanerges</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -7875,13 +7875,13 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -7889,27 +7889,27 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>alexandreconsentino</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -7917,83 +7917,83 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>rafaela_duaartee</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B202">
         <v>0</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>andre.legendre.10</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>phillipe.harry</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>andrejetx</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -8001,13 +8001,13 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>turmanmma</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -8015,13 +8015,13 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>gustavomohallem</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -8029,49 +8029,49 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>marinealcausa</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B210">
         <v>0</v>
       </c>
       <c r="C210">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>luizcosta_mma</v>
+        <v>coutz11</v>
       </c>
       <c r="B211">
         <v>0</v>
       </c>
       <c r="C211">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>cristianpsicologo</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B212">
         <v>0</v>
       </c>
       <c r="C212">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>giulia.fasolato</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B213">
         <v>0</v>
@@ -8080,46 +8080,46 @@
         <v>2</v>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>michelle_mirele</v>
+        <v>ommariotti</v>
       </c>
       <c r="B214">
         <v>0</v>
       </c>
       <c r="C214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>danielfranzesilva</v>
+        <v>brodschack_</v>
       </c>
       <c r="B215">
         <v>0</v>
       </c>
       <c r="C215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>ednilsonkaicai</v>
+        <v>_vpft</v>
       </c>
       <c r="B216">
         <v>0</v>
       </c>
       <c r="C216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -8127,13 +8127,13 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>emersonriosmma</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B217">
         <v>0</v>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -8141,21 +8141,21 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B218">
         <v>0</v>
       </c>
       <c r="C218">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>vanessamelomma</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B219">
         <v>0</v>
@@ -8164,12 +8164,12 @@
         <v>1</v>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>leonardopateira</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B220">
         <v>0</v>
@@ -8178,12 +8178,12 @@
         <v>1</v>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>rahikikhalid</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -8192,18 +8192,18 @@
         <v>1</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>manumito.oficial</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B222">
         <v>0</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -8211,13 +8211,13 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>carlosnoelblack</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B223">
         <v>0</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -8225,13 +8225,13 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>vanemessina</v>
       </c>
       <c r="B224">
         <v>0</v>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -8239,7 +8239,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>lokomemo_protetores</v>
+        <v>dadwillians</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -8248,12 +8248,12 @@
         <v>1</v>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>coutz11</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -8262,18 +8262,18 @@
         <v>1</v>
       </c>
       <c r="D226">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>orlando_alfa09</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B227">
         <v>0</v>
       </c>
       <c r="C227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -8281,13 +8281,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>vitorshowman</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
       <c r="C228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>pauloserrati</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -8304,18 +8304,18 @@
         <v>1</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>4lissson</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B230">
         <v>0</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>ommariotti</v>
+        <v>dandraco_</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -8332,12 +8332,12 @@
         <v>1</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>brodschack_</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8346,12 +8346,12 @@
         <v>1</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>_vpft</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8360,12 +8360,12 @@
         <v>1</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>helenaseveribjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>_kainanlima</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>jimmy_indioap</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>omar_alneaimi</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>victor_brunopersonal</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>motumbo_team</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>vanemessina</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>dadwillians</v>
+        <v>doraasivla</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>thalytabjj</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8505,7 +8505,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8519,7 +8519,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>esteticaluharruda</v>
+        <v>caioparangole</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8533,7 +8533,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>chubotaru_lilu</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8547,7 +8547,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>eusoufernandosaito</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>dandraco_</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8575,7 +8575,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>sejamotivadorofc</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>tpapereira</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8617,7 +8617,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>kfcampeoes</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>herrickmarinho</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>rafaelcmjj</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>cristianomarcello</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>_gabrielpego</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8687,7 +8687,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>taylor_71kg</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8715,7 +8715,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>doraasivla</v>
+        <v>couragemma</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>pe.mirandas</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -8743,7 +8743,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>leaoanaalice</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -8757,7 +8757,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>caioparangole</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>sabrinaalsilva</v>
+        <v>armysenju</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -8780,376 +8780,12 @@
         <v>1</v>
       </c>
       <c r="D263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="str">
-        <v>nuncadesistir.nd</v>
-      </c>
-      <c r="B264">
-        <v>0</v>
-      </c>
-      <c r="C264">
-        <v>1</v>
-      </c>
-      <c r="D264">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="str">
-        <v>eglaudiomma</v>
-      </c>
-      <c r="B265">
-        <v>0</v>
-      </c>
-      <c r="C265">
-        <v>1</v>
-      </c>
-      <c r="D265">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="str">
-        <v>strong_stg_oficial</v>
-      </c>
-      <c r="B266">
-        <v>0</v>
-      </c>
-      <c r="C266">
-        <v>1</v>
-      </c>
-      <c r="D266">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="str">
-        <v>ricardotofanello</v>
-      </c>
-      <c r="B267">
-        <v>0</v>
-      </c>
-      <c r="C267">
-        <v>1</v>
-      </c>
-      <c r="D267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="str">
-        <v>taporondebruno</v>
-      </c>
-      <c r="B268">
-        <v>0</v>
-      </c>
-      <c r="C268">
-        <v>1</v>
-      </c>
-      <c r="D268">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>anamatias.m</v>
-      </c>
-      <c r="B269">
-        <v>0</v>
-      </c>
-      <c r="C269">
-        <v>1</v>
-      </c>
-      <c r="D269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v>claudio_marchese_7</v>
-      </c>
-      <c r="B270">
-        <v>0</v>
-      </c>
-      <c r="C270">
-        <v>1</v>
-      </c>
-      <c r="D270">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="str">
-        <v>1000ton_n</v>
-      </c>
-      <c r="B271">
-        <v>0</v>
-      </c>
-      <c r="C271">
-        <v>1</v>
-      </c>
-      <c r="D271">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="str">
-        <v>paulo.titoo</v>
-      </c>
-      <c r="B272">
-        <v>0</v>
-      </c>
-      <c r="C272">
-        <v>1</v>
-      </c>
-      <c r="D272">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="str">
-        <v>vitorcosta_mma</v>
-      </c>
-      <c r="B273">
-        <v>0</v>
-      </c>
-      <c r="C273">
-        <v>1</v>
-      </c>
-      <c r="D273">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="str">
-        <v>dayanaa1511</v>
-      </c>
-      <c r="B274">
-        <v>0</v>
-      </c>
-      <c r="C274">
-        <v>1</v>
-      </c>
-      <c r="D274">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="str">
-        <v>couragemma</v>
-      </c>
-      <c r="B275">
-        <v>0</v>
-      </c>
-      <c r="C275">
-        <v>1</v>
-      </c>
-      <c r="D275">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="str">
-        <v>romulerasilva</v>
-      </c>
-      <c r="B276">
-        <v>0</v>
-      </c>
-      <c r="C276">
-        <v>1</v>
-      </c>
-      <c r="D276">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="str">
-        <v>edergama.mma</v>
-      </c>
-      <c r="B277">
-        <v>0</v>
-      </c>
-      <c r="C277">
-        <v>1</v>
-      </c>
-      <c r="D277">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="str">
-        <v>select_from_joao</v>
-      </c>
-      <c r="B278">
-        <v>0</v>
-      </c>
-      <c r="C278">
-        <v>1</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="str">
-        <v>alineanne_</v>
-      </c>
-      <c r="B279">
-        <v>0</v>
-      </c>
-      <c r="C279">
-        <v>1</v>
-      </c>
-      <c r="D279">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="str">
-        <v>julckreis</v>
-      </c>
-      <c r="B280">
-        <v>0</v>
-      </c>
-      <c r="C280">
-        <v>1</v>
-      </c>
-      <c r="D280">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="str">
-        <v>alexsandra_kairos</v>
-      </c>
-      <c r="B281">
-        <v>0</v>
-      </c>
-      <c r="C281">
-        <v>1</v>
-      </c>
-      <c r="D281">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="str">
-        <v>andreza.thais.1</v>
-      </c>
-      <c r="B282">
-        <v>0</v>
-      </c>
-      <c r="C282">
-        <v>1</v>
-      </c>
-      <c r="D282">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="str">
-        <v>benicius_edu</v>
-      </c>
-      <c r="B283">
-        <v>0</v>
-      </c>
-      <c r="C283">
-        <v>1</v>
-      </c>
-      <c r="D283">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="str">
-        <v>nataliaemanuela.personal</v>
-      </c>
-      <c r="B284">
-        <v>0</v>
-      </c>
-      <c r="C284">
-        <v>1</v>
-      </c>
-      <c r="D284">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="str">
-        <v>michele_mixa</v>
-      </c>
-      <c r="B285">
-        <v>0</v>
-      </c>
-      <c r="C285">
-        <v>1</v>
-      </c>
-      <c r="D285">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="str">
-        <v>joaolauar_</v>
-      </c>
-      <c r="B286">
-        <v>0</v>
-      </c>
-      <c r="C286">
-        <v>1</v>
-      </c>
-      <c r="D286">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="str">
-        <v>meirelesmma</v>
-      </c>
-      <c r="B287">
-        <v>0</v>
-      </c>
-      <c r="C287">
-        <v>1</v>
-      </c>
-      <c r="D287">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="str">
-        <v>dvlucc2k26_</v>
-      </c>
-      <c r="B288">
-        <v>0</v>
-      </c>
-      <c r="C288">
-        <v>1</v>
-      </c>
-      <c r="D288">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="str">
-        <v>armysenju</v>
-      </c>
-      <c r="B289">
-        <v>0</v>
-      </c>
-      <c r="C289">
-        <v>1</v>
-      </c>
-      <c r="D289">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D289"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D263"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>835</v>
+        <v>844</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -657,7 +657,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -2026,13 +2026,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B117">
         <v>1</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,13 +2054,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -2068,30 +2068,30 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>816</v>
+        <v>825</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5134,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4">
@@ -5148,13 +5148,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -5232,13 +5232,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -5358,7 +5358,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -6489,13 +6489,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -6503,13 +6503,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6517,7 +6517,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -6531,13 +6531,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -6545,30 +6545,30 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>030sami</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1087</v>
+        <v>1112</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>844</v>
+        <v>869</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -503,13 +503,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -598,38 +598,38 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>bellsouza816</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B15">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B16">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>kaua_limamma</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B17">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -640,21 +640,21 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>mmmarc20</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B18">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>hugo7jj</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B19">
         <v>33</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -688,7 +688,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D21">
         <v>34</v>
@@ -696,30 +696,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aline.r15</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>cleyton_jesuss</v>
+        <v>aline.r15</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -962,83 +962,83 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>gdazuera</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>enzoferrari680</v>
+        <v>gdazuera</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1060,16 +1060,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>badboykillermma</v>
+        <v>paxlucta</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1049</v>
+        <v>1074</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>825</v>
+        <v>850</v>
       </c>
     </row>
     <row r="3">
@@ -5162,13 +5162,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5204,13 +5204,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -5218,13 +5218,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B9">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5232,13 +5232,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -5285,52 +5285,52 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>bellsouza816</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ryangandraufc</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B15">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C15">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>erik_.mma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B16">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>kaua_limamma</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B17">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5341,21 +5341,21 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>mmmarc20</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B18">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>hugo7jj</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B19">
         <v>33</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -5400,13 +5400,13 @@
         <v>cleyton_jesuss</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
       <c r="D22">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -5417,7 +5417,7 @@
         <v>4</v>
       </c>
       <c r="C23">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D23">
         <v>31</v>
@@ -5621,100 +5621,100 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>enzoferrari680</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B39">
         <v>6</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>italothearcher</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>italothearcher</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>rrafaelins</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>paxlucta</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>badboykillermma</v>
+        <v>paxlucta</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>869</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -682,30 +682,30 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>god.motivacao</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>cleyton_jesuss</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B22">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>850</v>
+        <v>855</v>
       </c>
     </row>
     <row r="3">
@@ -5134,13 +5134,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
@@ -5148,13 +5148,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -5232,13 +5232,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -5383,30 +5383,30 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>aline.r15</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>cleyton_jesuss</v>
+        <v>aline.r15</v>
       </c>
       <c r="B22">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>874</v>
+        <v>879</v>
       </c>
     </row>
     <row r="3">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +545,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>855</v>
+        <v>860</v>
       </c>
     </row>
     <row r="3">
@@ -5232,13 +5232,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -5246,13 +5246,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B11">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">

--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -5099,7 +5099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D263"/>
+  <dimension ref="A1:D258"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5120,41 +5120,41 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1084</v>
+        <v>1057</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>860</v>
+        <v>848</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>quemuel_ottoni</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B3">
-        <v>221</v>
+        <v>309</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>313</v>
+        <v>177</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5">
@@ -5162,13 +5162,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -5176,7 +5176,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B6">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5190,13 +5190,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -5204,13 +5204,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -5313,30 +5313,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ryangandraufc</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>erik_.mma</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B17">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -5417,7 +5417,7 @@
         <v>4</v>
       </c>
       <c r="C23">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23">
         <v>31</v>
@@ -5439,30 +5439,30 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>gra_jpereira</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B25">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>alvesmidih</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -5512,13 +5512,13 @@
         <v>lucasluiz911_mma</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -5526,10 +5526,10 @@
         <v>tabajaraharu</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -5537,13 +5537,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>pedromadeira.s</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -5551,27 +5551,27 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>_beegomes_</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
         <v>7</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -5579,69 +5579,69 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>tawanregismma</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B35">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>vndcardoso</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>juniordiasmma</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>badboykillermma</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>enzoferrari680</v>
+        <v>italothearcher</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -5649,10 +5649,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -5663,27 +5663,27 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>italothearcher</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>paxlucta</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -5691,13 +5691,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>rrafaelins</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -5705,27 +5705,27 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>paxlucta</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>_.maduoliveira_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -5733,83 +5733,83 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>gdazuera</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>glm.barbosa</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>_oliveira09_</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49">
         <v>3</v>
       </c>
-      <c r="C49">
-        <v>5</v>
-      </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>marcelogabrielmma</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>eolucasrosa</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -5817,44 +5817,44 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>gabrielsouzamma</v>
+        <v>gdazuera</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ravenrodriguez___</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fabinho_falcao_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5865,7 +5865,7 @@
         <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -5873,35 +5873,35 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>mah__vergueiro</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>marcos_tailandess</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>lipe.ftt</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B58">
         <v>4</v>
@@ -5915,35 +5915,35 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>fau_gfs</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>dagestan0920</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ninjatheorist</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -5952,12 +5952,12 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>shawlin13oficial</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -5971,7 +5971,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>eduardorodrigrs</v>
+        <v>febrancatti</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -5999,27 +5999,27 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>febrancatti</v>
+        <v>reifernandes</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>dogodoyfoto</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -6027,119 +6027,119 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>reifernandes</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>daniel_dias_214</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>f.luan_11</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>vitorpetrino</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>jcchagas_</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>odeivisoncardoso</v>
+        <v>edebetim_</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
         <v>3</v>
-      </c>
-      <c r="D72">
-        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>maca.mariotti</v>
+        <v>s__simone__</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>edebetim_</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>s__simone__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -6153,55 +6153,55 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>kaua_limaofc</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>clouddhidden</v>
+        <v>ruangzk</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>lucascardosol__</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ruangzk</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -6209,27 +6209,27 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>adriano.trator</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ismaeldaniell</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B81">
         <v>2</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -6237,21 +6237,21 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>douglasipvr_mma</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>tassiogiloficial</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -6265,63 +6265,63 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>vnciuss__df</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>jhee_dias</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fredoctmma</v>
+        <v>joegam3r</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>fabaotipster</v>
+        <v>orafao1</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>joegam3r</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -6335,35 +6335,35 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>orafao1</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabi.godooy</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>leobahiamma</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>heltoncm2002</v>
+        <v>graalino</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -6419,7 +6419,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>raelduraes</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>graalino</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>lopesbrunao</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -6461,21 +6461,21 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>pedrinhosbjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>treinaadorrafael</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -6489,13 +6489,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>benjafloripabjj</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -6503,13 +6503,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fernando.mma</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -6517,13 +6517,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>030sami</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -6531,27 +6531,27 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fagnerosensei</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>030sami</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -6559,21 +6559,21 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>guiiviieira_</v>
+        <v>cshigueo</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -6587,7 +6587,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>cshigueo</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -6615,7 +6615,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>emerson_lucaszx</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>danni_goncalves12</v>
+        <v>mttsm._</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>mttsm._</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>andrealvess02</v>
+        <v>gildojiu</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -6671,7 +6671,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>gildojiu</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>kawannsennast</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>matheusteodoro_1</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>tonketjudes</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>_eliasffx</v>
+        <v>pdfiv</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>pdfiv</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -6755,7 +6755,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mariaraimundad940</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gabesantos.13</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>euvitormirandaa</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>thompsonborralho</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>frankikolimabjj</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>alerrandrojj</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -6839,35 +6839,35 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>mimuniz.bjj</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>diegopaivajj</v>
+        <v>anahangelica</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>anahangelica</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>minotaurinho</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>lara.rpr</v>
+        <v>codasqueves</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>codasqueves</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>yan_touro.7766</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>carolinne.xwp</v>
+        <v>davicorbella</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>davicorbella</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>artemio_bjj</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>katiaecarreraf</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -7035,35 +7035,35 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>geraldocnetomma</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>pedro_pavin_</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>karen.ottoni</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>xavyeroficial</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>maryanagandra</v>
+        <v>eliandropires</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>eliandropires</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>charlesanthony2466</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>draanapaulaponceano</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>saj_photo_miami</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -7175,7 +7175,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>alternativaremocoes</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>benivalentinn</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>navarro_9430</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -7231,7 +7231,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>_puroosso88</v>
+        <v>_rayysp</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>_rayysp</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>cami.terra_</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>gabicardoson</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>martta.mariah</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>wlt_miguel</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>jaonevesz</v>
+        <v>pietroshz</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>pietroshz</v>
+        <v>___neller</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>___neller</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>_bety_marcal</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pativinisf</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>pativinisf</v>
+        <v>judadany</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>judadany</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>andre_alcausa</v>
+        <v>_fernunes</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>_fernunes</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>aloirmarcal</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>gilberto_7606</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>flazuera14</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>camii_bonfim</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>danlouiz.jj</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gabriel_trevelin</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>y.arthur_01</v>
+        <v>muricunha</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7567,7 +7567,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>muricunha</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>victorhenriquebjj</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>_lsanchess_</v>
+        <v>__bielgg</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>__bielgg</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7623,7 +7623,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>mr__rlk01</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>vitor_buck</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>fran.ruys</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>wesley_bjjvc</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>sambagabrieloficial</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>peacegrappler</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7721,13 +7721,13 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>aliferpaulo_</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -7735,7 +7735,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>_alcantara.bru</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7749,13 +7749,13 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>rafaela_duaartee</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C190">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>turmanmma</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7791,13 +7791,13 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>turmanmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -7805,97 +7805,97 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gustavomohallem</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>marinealcausa</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B195">
         <v>0</v>
       </c>
       <c r="C195">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>luizcosta_mma</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B196">
         <v>0</v>
       </c>
       <c r="C196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>giulia.fasolato</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B197">
         <v>0</v>
       </c>
       <c r="C197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D197">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>michelle_mirele</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B198">
         <v>0</v>
       </c>
       <c r="C198">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>danielfranzesilva</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B199">
         <v>0</v>
       </c>
       <c r="C199">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>ednilsonkaicai</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B200">
         <v>0</v>
       </c>
       <c r="C200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -7903,27 +7903,27 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>emersonriosmma</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B201">
         <v>0</v>
       </c>
       <c r="C201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B202">
         <v>0</v>
       </c>
       <c r="C202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>cristianpsicologo</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -7940,82 +7940,82 @@
         <v>2</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>vanessamelomma</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B204">
         <v>0</v>
       </c>
       <c r="C204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>leonardopateira</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B205">
         <v>0</v>
       </c>
       <c r="C205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>rahikikhalid</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B206">
         <v>0</v>
       </c>
       <c r="C206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>manumito.oficial</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B207">
         <v>0</v>
       </c>
       <c r="C207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>carlosnoelblack</v>
+        <v>coutz11</v>
       </c>
       <c r="B208">
         <v>0</v>
       </c>
       <c r="C208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -8029,21 +8029,21 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>lokomemo_protetores</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B210">
         <v>0</v>
       </c>
       <c r="C210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>coutz11</v>
+        <v>ommariotti</v>
       </c>
       <c r="B211">
         <v>0</v>
@@ -8057,35 +8057,35 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>orlando_alfa09</v>
+        <v>brodschack_</v>
       </c>
       <c r="B212">
         <v>0</v>
       </c>
       <c r="C212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>vitorshowman</v>
+        <v>_vpft</v>
       </c>
       <c r="B213">
         <v>0</v>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>ommariotti</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B214">
         <v>0</v>
@@ -8094,12 +8094,12 @@
         <v>1</v>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>brodschack_</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B215">
         <v>0</v>
@@ -8108,12 +8108,12 @@
         <v>1</v>
       </c>
       <c r="D215">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>_vpft</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B216">
         <v>0</v>
@@ -8122,12 +8122,12 @@
         <v>1</v>
       </c>
       <c r="D216">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B217">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>helenaseveribjj</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B218">
         <v>0</v>
@@ -8155,7 +8155,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>_kainanlima</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B219">
         <v>0</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>jimmy_indioap</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B220">
         <v>0</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>omar_alneaimi</v>
+        <v>vanemessina</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -8197,7 +8197,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>victor_brunopersonal</v>
+        <v>dadwillians</v>
       </c>
       <c r="B222">
         <v>0</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>motumbo_team</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B223">
         <v>0</v>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>vanemessina</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -8239,7 +8239,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>dadwillians</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>thalytabjj</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -8281,7 +8281,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>esteticaluharruda</v>
+        <v>dandraco_</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>chubotaru_lilu</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -8309,7 +8309,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>eusoufernandosaito</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>dandraco_</v>
+        <v>tpapereira</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>sejamotivadorofc</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>tpapereira</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>kfcampeoes</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>herrickmarinho</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>rafaelcmjj</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>cristianomarcello</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>_gabrielpego</v>
+        <v>doraasivla</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>taylor_71kg</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>doraasivla</v>
+        <v>caioparangole</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>pe.mirandas</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -8505,7 +8505,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>leaoanaalice</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -8519,7 +8519,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>caioparangole</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -8533,7 +8533,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>sabrinaalsilva</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -8547,7 +8547,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>eglaudiomma</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -8575,7 +8575,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>strong_stg_oficial</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ricardotofanello</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>taporondebruno</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -8617,7 +8617,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>washington_cassisno</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>anamatias.m</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>claudio_marchese_7</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>1000ton_n</v>
+        <v>couragemma</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>paulo.titoo</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -8687,7 +8687,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>vitorcosta_mma</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>dayanaa1511</v>
+        <v>armysenju</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -8710,82 +8710,12 @@
         <v>1</v>
       </c>
       <c r="D258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="str">
-        <v>couragemma</v>
-      </c>
-      <c r="B259">
-        <v>0</v>
-      </c>
-      <c r="C259">
-        <v>1</v>
-      </c>
-      <c r="D259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="str">
-        <v>romulerasilva</v>
-      </c>
-      <c r="B260">
-        <v>0</v>
-      </c>
-      <c r="C260">
-        <v>1</v>
-      </c>
-      <c r="D260">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="str">
-        <v>meirelesmma</v>
-      </c>
-      <c r="B261">
-        <v>0</v>
-      </c>
-      <c r="C261">
-        <v>1</v>
-      </c>
-      <c r="D261">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="str">
-        <v>dvlucc2k26_</v>
-      </c>
-      <c r="B262">
-        <v>0</v>
-      </c>
-      <c r="C262">
-        <v>1</v>
-      </c>
-      <c r="D262">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="str">
-        <v>armysenju</v>
-      </c>
-      <c r="B263">
-        <v>0</v>
-      </c>
-      <c r="C263">
-        <v>1</v>
-      </c>
-      <c r="D263">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D258"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community Engagement Rankings.xlsx
+++ b/Community Engagement Rankings.xlsx
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1122</v>
+        <v>1134</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>879</v>
+        <v>891</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B13">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>33</v>
@@ -584,30 +584,30 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ronemayanmorais</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>hugo7jj</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B15">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -850,27 +850,27 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B33">
         <v>8</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>tawanregismma</v>
+        <v>maxgandra</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -878,7 +878,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>_beegomes_</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -5120,13 +5120,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>848</v>
+        <v>860</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
     